--- a/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/08,26/04,08,26 ПОКОМ КИ/дв 04,08,26 лгрсч пок ки.xlsx
+++ b/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/08,26/04,08,26 ПОКОМ КИ/дв 04,08,26 лгрсч пок ки.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты ПОКОМ КИ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\08,26\04,08,26 ПОКОМ КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3C9A50B-8141-4AB0-AEBA-C03DB8776653}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02DE0A00-C629-4FD9-94CE-0D4D51A1F479}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,15 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AJ$135</definedName>
   </definedNames>
-  <calcPr calcId="181029" refMode="R1C1"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029" refMode="R1C1"/>
 </workbook>
 </file>
 
@@ -612,17 +604,23 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="10"/>
@@ -634,6 +632,8 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
@@ -727,7 +727,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -747,14 +747,7 @@
     <xf numFmtId="164" fontId="1" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -1073,7 +1066,7 @@
     <col min="11" max="12" width="7" customWidth="1"/>
     <col min="13" max="14" width="0.5703125" customWidth="1"/>
     <col min="15" max="21" width="7" customWidth="1"/>
-    <col min="22" max="22" width="7" style="21" customWidth="1"/>
+    <col min="22" max="22" width="7" style="19" customWidth="1"/>
     <col min="23" max="24" width="5" customWidth="1"/>
     <col min="25" max="25" width="6" customWidth="1"/>
     <col min="26" max="34" width="6.5703125" customWidth="1"/>
@@ -1545,7 +1538,7 @@
         <f>T6</f>
         <v>640.79170000000022</v>
       </c>
-      <c r="V6" s="19"/>
+      <c r="V6" s="1"/>
       <c r="W6" s="1">
         <f>(F6+O6+P6+Q6+R6+U6)/S6</f>
         <v>10.5</v>
@@ -1589,7 +1582,10 @@
         <f>ROUND(G6*U6,0)</f>
         <v>641</v>
       </c>
-      <c r="AK6" s="1"/>
+      <c r="AK6" s="1">
+        <f>(SUM(Y6:AH6)+S6)/11</f>
+        <v>535.10529090909085</v>
+      </c>
       <c r="AL6" s="1"/>
       <c r="AM6" s="1"/>
       <c r="AN6" s="1"/>
@@ -1650,7 +1646,7 @@
         <f t="shared" ref="U7:U70" si="5">T7</f>
         <v>0</v>
       </c>
-      <c r="V7" s="19"/>
+      <c r="V7" s="1"/>
       <c r="W7" s="1">
         <f t="shared" ref="W7:W70" si="6">(F7+O7+P7+Q7+R7+U7)/S7</f>
         <v>11.091843727140493</v>
@@ -1694,7 +1690,10 @@
         <f t="shared" ref="AJ7:AJ70" si="7">ROUND(G7*U7,0)</f>
         <v>0</v>
       </c>
-      <c r="AK7" s="1"/>
+      <c r="AK7" s="1">
+        <f t="shared" ref="AK7:AK70" si="8">(SUM(Y7:AH7)+S7)/11</f>
+        <v>245.07856363636364</v>
+      </c>
       <c r="AL7" s="1"/>
       <c r="AM7" s="1"/>
       <c r="AN7" s="1"/>
@@ -1755,7 +1754,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="V8" s="19"/>
+      <c r="V8" s="1"/>
       <c r="W8" s="1">
         <f t="shared" si="6"/>
         <v>11.437685673424642</v>
@@ -1799,7 +1798,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AK8" s="1"/>
+      <c r="AK8" s="1">
+        <f t="shared" si="8"/>
+        <v>234.09361818181821</v>
+      </c>
       <c r="AL8" s="1"/>
       <c r="AM8" s="1"/>
       <c r="AN8" s="1"/>
@@ -1848,7 +1850,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="V9" s="20"/>
+      <c r="V9" s="11"/>
       <c r="W9" s="1" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
@@ -1894,7 +1896,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AK9" s="1"/>
+      <c r="AK9" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="AL9" s="1"/>
       <c r="AM9" s="1"/>
       <c r="AN9" s="1"/>
@@ -1957,7 +1962,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="V10" s="19"/>
+      <c r="V10" s="1"/>
       <c r="W10" s="1">
         <f t="shared" si="6"/>
         <v>11.433447098976108</v>
@@ -2001,7 +2006,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AK10" s="1"/>
+      <c r="AK10" s="1">
+        <f t="shared" si="8"/>
+        <v>121.56363636363636</v>
+      </c>
       <c r="AL10" s="1"/>
       <c r="AM10" s="1"/>
       <c r="AN10" s="1"/>
@@ -2064,7 +2072,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="V11" s="19"/>
+      <c r="V11" s="1"/>
       <c r="W11" s="1">
         <f t="shared" si="6"/>
         <v>10.887577111252925</v>
@@ -2108,7 +2116,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AK11" s="1"/>
+      <c r="AK11" s="1">
+        <f t="shared" si="8"/>
+        <v>227.2225454545455</v>
+      </c>
       <c r="AL11" s="1"/>
       <c r="AM11" s="1"/>
       <c r="AN11" s="1"/>
@@ -2165,14 +2176,14 @@
         <v>17.2</v>
       </c>
       <c r="T12" s="5">
-        <f t="shared" ref="T12:T14" si="8">10.5*S12-R12-Q12-P12-O12-F12</f>
+        <f t="shared" ref="T12:T14" si="9">10.5*S12-R12-Q12-P12-O12-F12</f>
         <v>38.599999999999994</v>
       </c>
       <c r="U12" s="5">
         <f t="shared" si="5"/>
         <v>38.599999999999994</v>
       </c>
-      <c r="V12" s="19"/>
+      <c r="V12" s="1"/>
       <c r="W12" s="1">
         <f t="shared" si="6"/>
         <v>10.5</v>
@@ -2216,7 +2227,10 @@
         <f t="shared" si="7"/>
         <v>7</v>
       </c>
-      <c r="AK12" s="1"/>
+      <c r="AK12" s="1">
+        <f t="shared" si="8"/>
+        <v>14.254545454545452</v>
+      </c>
       <c r="AL12" s="1"/>
       <c r="AM12" s="1"/>
       <c r="AN12" s="1"/>
@@ -2273,14 +2287,14 @@
         <v>21</v>
       </c>
       <c r="T13" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>8.5000000000000284</v>
       </c>
       <c r="U13" s="5">
         <f t="shared" si="5"/>
         <v>8.5000000000000284</v>
       </c>
-      <c r="V13" s="19"/>
+      <c r="V13" s="1"/>
       <c r="W13" s="1">
         <f t="shared" si="6"/>
         <v>10.5</v>
@@ -2324,7 +2338,10 @@
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="AK13" s="1"/>
+      <c r="AK13" s="1">
+        <f t="shared" si="8"/>
+        <v>16.654545454545456</v>
+      </c>
       <c r="AL13" s="1"/>
       <c r="AM13" s="1"/>
       <c r="AN13" s="1"/>
@@ -2381,14 +2398,14 @@
         <v>52.8</v>
       </c>
       <c r="T14" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>206.39999999999998</v>
       </c>
       <c r="U14" s="5">
         <f t="shared" si="5"/>
         <v>206.39999999999998</v>
       </c>
-      <c r="V14" s="19"/>
+      <c r="V14" s="1"/>
       <c r="W14" s="1">
         <f t="shared" si="6"/>
         <v>10.5</v>
@@ -2432,7 +2449,10 @@
         <f t="shared" si="7"/>
         <v>35</v>
       </c>
-      <c r="AK14" s="1"/>
+      <c r="AK14" s="1">
+        <f t="shared" si="8"/>
+        <v>45.709090909090911</v>
+      </c>
       <c r="AL14" s="1"/>
       <c r="AM14" s="1"/>
       <c r="AN14" s="1"/>
@@ -2487,7 +2507,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="V15" s="20"/>
+      <c r="V15" s="11"/>
       <c r="W15" s="1">
         <f t="shared" si="6"/>
         <v>-5</v>
@@ -2531,7 +2551,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AK15" s="1"/>
+      <c r="AK15" s="1">
+        <f t="shared" si="8"/>
+        <v>3.6363636363636369E-2</v>
+      </c>
       <c r="AL15" s="1"/>
       <c r="AM15" s="1"/>
       <c r="AN15" s="1"/>
@@ -2590,10 +2613,10 @@
         <v>236.7696</v>
       </c>
       <c r="T16" s="5"/>
-      <c r="U16" s="27">
+      <c r="U16" s="20">
         <v>650</v>
       </c>
-      <c r="V16" s="19"/>
+      <c r="V16" s="1"/>
       <c r="W16" s="1">
         <f t="shared" si="6"/>
         <v>13.949699202093511</v>
@@ -2637,7 +2660,10 @@
         <f t="shared" si="7"/>
         <v>650</v>
       </c>
-      <c r="AK16" s="1"/>
+      <c r="AK16" s="1">
+        <f t="shared" si="8"/>
+        <v>228.66201818181815</v>
+      </c>
       <c r="AL16" s="1"/>
       <c r="AM16" s="1"/>
       <c r="AN16" s="1"/>
@@ -2694,10 +2720,10 @@
         <v>703.17060000000004</v>
       </c>
       <c r="T17" s="5"/>
-      <c r="U17" s="27">
+      <c r="U17" s="20">
         <v>700</v>
       </c>
-      <c r="V17" s="19"/>
+      <c r="V17" s="1"/>
       <c r="W17" s="1">
         <f t="shared" si="6"/>
         <v>14.494930533216262</v>
@@ -2741,7 +2767,10 @@
         <f t="shared" si="7"/>
         <v>700</v>
       </c>
-      <c r="AK17" s="1"/>
+      <c r="AK17" s="1">
+        <f t="shared" si="8"/>
+        <v>725.5826545454546</v>
+      </c>
       <c r="AL17" s="1"/>
       <c r="AM17" s="1"/>
       <c r="AN17" s="1"/>
@@ -2798,14 +2827,14 @@
         <v>24.598400000000002</v>
       </c>
       <c r="T18" s="5">
-        <f t="shared" ref="T18:T22" si="9">10.5*S18-R18-Q18-P18-O18-F18</f>
+        <f t="shared" ref="T18:T22" si="10">10.5*S18-R18-Q18-P18-O18-F18</f>
         <v>84.243200000000016</v>
       </c>
       <c r="U18" s="5">
         <f t="shared" si="5"/>
         <v>84.243200000000016</v>
       </c>
-      <c r="V18" s="19"/>
+      <c r="V18" s="1"/>
       <c r="W18" s="1">
         <f t="shared" si="6"/>
         <v>10.5</v>
@@ -2849,7 +2878,10 @@
         <f t="shared" si="7"/>
         <v>84</v>
       </c>
-      <c r="AK18" s="1"/>
+      <c r="AK18" s="1">
+        <f t="shared" si="8"/>
+        <v>20.341709090909088</v>
+      </c>
       <c r="AL18" s="1"/>
       <c r="AM18" s="1"/>
       <c r="AN18" s="1"/>
@@ -2912,7 +2944,7 @@
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="V19" s="19"/>
+      <c r="V19" s="1"/>
       <c r="W19" s="1">
         <f t="shared" si="6"/>
         <v>10.626597697698854</v>
@@ -2956,7 +2988,10 @@
         <f t="shared" si="7"/>
         <v>4</v>
       </c>
-      <c r="AK19" s="1"/>
+      <c r="AK19" s="1">
+        <f t="shared" si="8"/>
+        <v>15.501818181818182</v>
+      </c>
       <c r="AL19" s="1"/>
       <c r="AM19" s="1"/>
       <c r="AN19" s="1"/>
@@ -3013,14 +3048,14 @@
         <v>2.1626000000000003</v>
       </c>
       <c r="T20" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>5.4963000000000051</v>
       </c>
       <c r="U20" s="5">
         <f t="shared" si="5"/>
         <v>5.4963000000000051</v>
       </c>
-      <c r="V20" s="19"/>
+      <c r="V20" s="1"/>
       <c r="W20" s="1">
         <f t="shared" si="6"/>
         <v>10.5</v>
@@ -3064,7 +3099,10 @@
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
-      <c r="AK20" s="1"/>
+      <c r="AK20" s="1">
+        <f t="shared" si="8"/>
+        <v>1.4450727272727273</v>
+      </c>
       <c r="AL20" s="1"/>
       <c r="AM20" s="1"/>
       <c r="AN20" s="1"/>
@@ -3127,7 +3165,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="V21" s="19"/>
+      <c r="V21" s="1"/>
       <c r="W21" s="1">
         <f t="shared" si="6"/>
         <v>12.221978757421272</v>
@@ -3171,7 +3209,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AK21" s="1"/>
+      <c r="AK21" s="1">
+        <f t="shared" si="8"/>
+        <v>282.73099999999999</v>
+      </c>
       <c r="AL21" s="1"/>
       <c r="AM21" s="1"/>
       <c r="AN21" s="1"/>
@@ -3228,14 +3269,14 @@
         <v>37.6586</v>
       </c>
       <c r="T22" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>81.236300000000028</v>
       </c>
       <c r="U22" s="5">
         <f t="shared" si="5"/>
         <v>81.236300000000028</v>
       </c>
-      <c r="V22" s="19"/>
+      <c r="V22" s="1"/>
       <c r="W22" s="1">
         <f t="shared" si="6"/>
         <v>10.5</v>
@@ -3279,7 +3320,10 @@
         <f t="shared" si="7"/>
         <v>81</v>
       </c>
-      <c r="AK22" s="1"/>
+      <c r="AK22" s="1">
+        <f t="shared" si="8"/>
+        <v>37.053890909090917</v>
+      </c>
       <c r="AL22" s="1"/>
       <c r="AM22" s="1"/>
       <c r="AN22" s="1"/>
@@ -3340,7 +3384,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="V23" s="19"/>
+      <c r="V23" s="1"/>
       <c r="W23" s="1">
         <f t="shared" si="6"/>
         <v>12.104703789423159</v>
@@ -3384,7 +3428,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AK23" s="1"/>
+      <c r="AK23" s="1">
+        <f t="shared" si="8"/>
+        <v>92.673236363636363</v>
+      </c>
       <c r="AL23" s="1"/>
       <c r="AM23" s="1"/>
       <c r="AN23" s="1"/>
@@ -3433,7 +3480,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="V24" s="20"/>
+      <c r="V24" s="11"/>
       <c r="W24" s="1" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
@@ -3479,7 +3526,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AK24" s="1"/>
+      <c r="AK24" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="AL24" s="1"/>
       <c r="AM24" s="1"/>
       <c r="AN24" s="1"/>
@@ -3542,7 +3592,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="V25" s="19"/>
+      <c r="V25" s="1"/>
       <c r="W25" s="1">
         <f t="shared" si="6"/>
         <v>10.811815345048041</v>
@@ -3586,7 +3636,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AK25" s="1"/>
+      <c r="AK25" s="1">
+        <f t="shared" si="8"/>
+        <v>128.64598181818181</v>
+      </c>
       <c r="AL25" s="1"/>
       <c r="AM25" s="1"/>
       <c r="AN25" s="1"/>
@@ -3643,14 +3696,14 @@
         <v>30.359199999999998</v>
       </c>
       <c r="T26" s="5">
-        <f t="shared" ref="T26" si="10">10.5*S26-R26-Q26-P26-O26-F26</f>
+        <f t="shared" ref="T26" si="11">10.5*S26-R26-Q26-P26-O26-F26</f>
         <v>122.24859999999998</v>
       </c>
       <c r="U26" s="5">
         <f t="shared" si="5"/>
         <v>122.24859999999998</v>
       </c>
-      <c r="V26" s="19"/>
+      <c r="V26" s="1"/>
       <c r="W26" s="1">
         <f t="shared" si="6"/>
         <v>10.5</v>
@@ -3694,7 +3747,10 @@
         <f t="shared" si="7"/>
         <v>122</v>
       </c>
-      <c r="AK26" s="1"/>
+      <c r="AK26" s="1">
+        <f t="shared" si="8"/>
+        <v>14.142818181818178</v>
+      </c>
       <c r="AL26" s="1"/>
       <c r="AM26" s="1"/>
       <c r="AN26" s="1"/>
@@ -3755,7 +3811,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="V27" s="19"/>
+      <c r="V27" s="1"/>
       <c r="W27" s="1">
         <f t="shared" si="6"/>
         <v>14.027368416057332</v>
@@ -3799,7 +3855,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AK27" s="1"/>
+      <c r="AK27" s="1">
+        <f t="shared" si="8"/>
+        <v>51.29614545454546</v>
+      </c>
       <c r="AL27" s="1"/>
       <c r="AM27" s="1"/>
       <c r="AN27" s="1"/>
@@ -3862,7 +3921,7 @@
         <f t="shared" si="5"/>
         <v>100</v>
       </c>
-      <c r="V28" s="19"/>
+      <c r="V28" s="1"/>
       <c r="W28" s="1">
         <f t="shared" si="6"/>
         <v>6.0367109131746695</v>
@@ -3906,7 +3965,10 @@
         <f t="shared" si="7"/>
         <v>100</v>
       </c>
-      <c r="AK28" s="1"/>
+      <c r="AK28" s="1">
+        <f t="shared" si="8"/>
+        <v>40.588654545454546</v>
+      </c>
       <c r="AL28" s="1"/>
       <c r="AM28" s="1"/>
       <c r="AN28" s="1"/>
@@ -3969,7 +4031,7 @@
         <f t="shared" si="5"/>
         <v>500</v>
       </c>
-      <c r="V29" s="19"/>
+      <c r="V29" s="1"/>
       <c r="W29" s="1">
         <f t="shared" si="6"/>
         <v>6.2221328489988563</v>
@@ -4013,7 +4075,10 @@
         <f t="shared" si="7"/>
         <v>500</v>
       </c>
-      <c r="AK29" s="1"/>
+      <c r="AK29" s="1">
+        <f t="shared" si="8"/>
+        <v>392.35176363636361</v>
+      </c>
       <c r="AL29" s="1"/>
       <c r="AM29" s="1"/>
       <c r="AN29" s="1"/>
@@ -4072,7 +4137,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="V30" s="20"/>
+      <c r="V30" s="11"/>
       <c r="W30" s="1">
         <f t="shared" si="6"/>
         <v>0.37731340689894866</v>
@@ -4116,7 +4181,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AK30" s="1"/>
+      <c r="AK30" s="1">
+        <f t="shared" si="8"/>
+        <v>4.1091272727272727</v>
+      </c>
       <c r="AL30" s="1"/>
       <c r="AM30" s="1"/>
       <c r="AN30" s="1"/>
@@ -4175,7 +4243,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="V31" s="20"/>
+      <c r="V31" s="11"/>
       <c r="W31" s="1">
         <f t="shared" si="6"/>
         <v>-0.1983330760919895</v>
@@ -4219,7 +4287,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AK31" s="1"/>
+      <c r="AK31" s="1">
+        <f t="shared" si="8"/>
+        <v>9.5146727272727265</v>
+      </c>
       <c r="AL31" s="1"/>
       <c r="AM31" s="1"/>
       <c r="AN31" s="1"/>
@@ -4280,7 +4351,7 @@
         <f t="shared" si="5"/>
         <v>700</v>
       </c>
-      <c r="V32" s="19"/>
+      <c r="V32" s="1"/>
       <c r="W32" s="1">
         <f t="shared" si="6"/>
         <v>2.5795145383073814</v>
@@ -4324,7 +4395,10 @@
         <f t="shared" si="7"/>
         <v>700</v>
       </c>
-      <c r="AK32" s="1"/>
+      <c r="AK32" s="1">
+        <f t="shared" si="8"/>
+        <v>403.02340000000004</v>
+      </c>
       <c r="AL32" s="1"/>
       <c r="AM32" s="1"/>
       <c r="AN32" s="1"/>
@@ -4373,7 +4447,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="V33" s="20"/>
+      <c r="V33" s="11"/>
       <c r="W33" s="1" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
@@ -4419,7 +4493,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AK33" s="1"/>
+      <c r="AK33" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="AL33" s="1"/>
       <c r="AM33" s="1"/>
       <c r="AN33" s="1"/>
@@ -4483,7 +4560,7 @@
         <f t="shared" si="5"/>
         <v>170.95990000000006</v>
       </c>
-      <c r="V34" s="19"/>
+      <c r="V34" s="1"/>
       <c r="W34" s="1">
         <f t="shared" si="6"/>
         <v>10.5</v>
@@ -4527,7 +4604,10 @@
         <f t="shared" si="7"/>
         <v>171</v>
       </c>
-      <c r="AK34" s="1"/>
+      <c r="AK34" s="1">
+        <f t="shared" si="8"/>
+        <v>47.696836363636365</v>
+      </c>
       <c r="AL34" s="1"/>
       <c r="AM34" s="1"/>
       <c r="AN34" s="1"/>
@@ -4576,7 +4656,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="V35" s="20"/>
+      <c r="V35" s="11"/>
       <c r="W35" s="1" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
@@ -4622,7 +4702,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AK35" s="1"/>
+      <c r="AK35" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="AL35" s="1"/>
       <c r="AM35" s="1"/>
       <c r="AN35" s="1"/>
@@ -4671,7 +4754,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="V36" s="20"/>
+      <c r="V36" s="11"/>
       <c r="W36" s="1" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
@@ -4717,7 +4800,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AK36" s="1"/>
+      <c r="AK36" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="AL36" s="1"/>
       <c r="AM36" s="1"/>
       <c r="AN36" s="1"/>
@@ -4780,7 +4866,7 @@
         <f t="shared" si="5"/>
         <v>1000</v>
       </c>
-      <c r="V37" s="19"/>
+      <c r="V37" s="1"/>
       <c r="W37" s="1">
         <f t="shared" si="6"/>
         <v>7.0263243218839904</v>
@@ -4824,7 +4910,10 @@
         <f t="shared" si="7"/>
         <v>400</v>
       </c>
-      <c r="AK37" s="1"/>
+      <c r="AK37" s="1">
+        <f t="shared" si="8"/>
+        <v>896.28447272727271</v>
+      </c>
       <c r="AL37" s="1"/>
       <c r="AM37" s="1"/>
       <c r="AN37" s="1"/>
@@ -4865,7 +4954,7 @@
         <v>392</v>
       </c>
       <c r="L38" s="1">
-        <f t="shared" ref="L38:L69" si="11">E38-K38</f>
+        <f t="shared" ref="L38:L69" si="12">E38-K38</f>
         <v>-17</v>
       </c>
       <c r="M38" s="1"/>
@@ -4877,7 +4966,7 @@
       </c>
       <c r="R38" s="1"/>
       <c r="S38" s="1">
-        <f t="shared" ref="S38:S69" si="12">E38/5</f>
+        <f t="shared" ref="S38:S69" si="13">E38/5</f>
         <v>75</v>
       </c>
       <c r="T38" s="5"/>
@@ -4885,13 +4974,13 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="V38" s="19"/>
+      <c r="V38" s="1"/>
       <c r="W38" s="1">
         <f t="shared" si="6"/>
         <v>10.933333333333334</v>
       </c>
       <c r="X38" s="1">
-        <f t="shared" ref="X38:X69" si="13">(F38+O38+P38+Q38+R38)/S38</f>
+        <f t="shared" ref="X38:X69" si="14">(F38+O38+P38+Q38+R38)/S38</f>
         <v>10.933333333333334</v>
       </c>
       <c r="Y38" s="1">
@@ -4929,7 +5018,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AK38" s="1"/>
+      <c r="AK38" s="1">
+        <f t="shared" si="8"/>
+        <v>91.327272727272742</v>
+      </c>
       <c r="AL38" s="1"/>
       <c r="AM38" s="1"/>
       <c r="AN38" s="1"/>
@@ -4970,7 +5062,7 @@
         <v>957</v>
       </c>
       <c r="L39" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-129</v>
       </c>
       <c r="M39" s="1"/>
@@ -4984,7 +5076,7 @@
       </c>
       <c r="R39" s="1"/>
       <c r="S39" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>165.6</v>
       </c>
       <c r="T39" s="5">
@@ -4994,13 +5086,13 @@
         <f t="shared" si="5"/>
         <v>200</v>
       </c>
-      <c r="V39" s="19"/>
+      <c r="V39" s="1"/>
       <c r="W39" s="1">
         <f t="shared" si="6"/>
         <v>8.520531400966183</v>
       </c>
       <c r="X39" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>7.31280193236715</v>
       </c>
       <c r="Y39" s="1">
@@ -5038,7 +5130,10 @@
         <f t="shared" si="7"/>
         <v>80</v>
       </c>
-      <c r="AK39" s="1"/>
+      <c r="AK39" s="1">
+        <f t="shared" si="8"/>
+        <v>203</v>
+      </c>
       <c r="AL39" s="1"/>
       <c r="AM39" s="1"/>
       <c r="AN39" s="1"/>
@@ -5079,7 +5174,7 @@
         <v>17</v>
       </c>
       <c r="L40" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-6</v>
       </c>
       <c r="M40" s="1"/>
@@ -5091,7 +5186,7 @@
       </c>
       <c r="R40" s="1"/>
       <c r="S40" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>2.2000000000000002</v>
       </c>
       <c r="T40" s="5"/>
@@ -5099,13 +5194,13 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="V40" s="19"/>
+      <c r="V40" s="1"/>
       <c r="W40" s="1">
         <f t="shared" si="6"/>
         <v>22.727272727272727</v>
       </c>
       <c r="X40" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>22.727272727272727</v>
       </c>
       <c r="Y40" s="1">
@@ -5143,7 +5238,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AK40" s="1"/>
+      <c r="AK40" s="1">
+        <f t="shared" si="8"/>
+        <v>2.4</v>
+      </c>
       <c r="AL40" s="1"/>
       <c r="AM40" s="1"/>
       <c r="AN40" s="1"/>
@@ -5184,7 +5282,7 @@
         <v>231.25</v>
       </c>
       <c r="L41" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-41.537000000000006</v>
       </c>
       <c r="M41" s="1"/>
@@ -5196,7 +5294,7 @@
       </c>
       <c r="R41" s="1"/>
       <c r="S41" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>37.942599999999999</v>
       </c>
       <c r="T41" s="5"/>
@@ -5204,13 +5302,13 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="V41" s="19"/>
+      <c r="V41" s="1"/>
       <c r="W41" s="1">
         <f t="shared" si="6"/>
         <v>14.512632239224514</v>
       </c>
       <c r="X41" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>14.512632239224514</v>
       </c>
       <c r="Y41" s="1">
@@ -5248,7 +5346,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AK41" s="1"/>
+      <c r="AK41" s="1">
+        <f t="shared" si="8"/>
+        <v>55.282181818181812</v>
+      </c>
       <c r="AL41" s="1"/>
       <c r="AM41" s="1"/>
       <c r="AN41" s="1"/>
@@ -5287,7 +5388,7 @@
         <v>393</v>
       </c>
       <c r="L42" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M42" s="1"/>
@@ -5299,24 +5400,24 @@
       </c>
       <c r="R42" s="1"/>
       <c r="S42" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>78.599999999999994</v>
       </c>
       <c r="T42" s="5">
-        <f t="shared" ref="T42:T53" si="14">10.5*S42-R42-Q42-P42-O42-F42</f>
+        <f t="shared" ref="T42:T53" si="15">10.5*S42-R42-Q42-P42-O42-F42</f>
         <v>23.311000000000035</v>
       </c>
       <c r="U42" s="5">
         <f t="shared" si="5"/>
         <v>23.311000000000035</v>
       </c>
-      <c r="V42" s="19"/>
+      <c r="V42" s="1"/>
       <c r="W42" s="1">
         <f t="shared" si="6"/>
         <v>10.5</v>
       </c>
       <c r="X42" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>10.203422391857506</v>
       </c>
       <c r="Y42" s="1">
@@ -5354,7 +5455,10 @@
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
-      <c r="AK42" s="1"/>
+      <c r="AK42" s="1">
+        <f t="shared" si="8"/>
+        <v>59.745454545454542</v>
+      </c>
       <c r="AL42" s="1"/>
       <c r="AM42" s="1"/>
       <c r="AN42" s="1"/>
@@ -5391,7 +5495,7 @@
         <v>213</v>
       </c>
       <c r="L43" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-71</v>
       </c>
       <c r="M43" s="1"/>
@@ -5403,24 +5507,24 @@
       </c>
       <c r="R43" s="1"/>
       <c r="S43" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>28.4</v>
       </c>
       <c r="T43" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>49.855999999999881</v>
       </c>
       <c r="U43" s="5">
         <f t="shared" si="5"/>
         <v>49.855999999999881</v>
       </c>
-      <c r="V43" s="19"/>
+      <c r="V43" s="1"/>
       <c r="W43" s="1">
         <f t="shared" si="6"/>
         <v>10.5</v>
       </c>
       <c r="X43" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>8.7445070422535256</v>
       </c>
       <c r="Y43" s="1">
@@ -5458,7 +5562,10 @@
         <f t="shared" si="7"/>
         <v>17</v>
       </c>
-      <c r="AK43" s="1"/>
+      <c r="AK43" s="1">
+        <f t="shared" si="8"/>
+        <v>47.327272727272728</v>
+      </c>
       <c r="AL43" s="1"/>
       <c r="AM43" s="1"/>
       <c r="AN43" s="1"/>
@@ -5499,7 +5606,7 @@
         <v>48.3</v>
       </c>
       <c r="L44" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-7.5389999999999944</v>
       </c>
       <c r="M44" s="1"/>
@@ -5511,7 +5618,7 @@
       </c>
       <c r="R44" s="1"/>
       <c r="S44" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>8.1522000000000006</v>
       </c>
       <c r="T44" s="5"/>
@@ -5519,13 +5626,13 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="V44" s="19"/>
+      <c r="V44" s="1"/>
       <c r="W44" s="1">
         <f t="shared" si="6"/>
         <v>13.636981428326092</v>
       </c>
       <c r="X44" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>13.636981428326092</v>
       </c>
       <c r="Y44" s="1">
@@ -5563,7 +5670,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AK44" s="1"/>
+      <c r="AK44" s="1">
+        <f t="shared" si="8"/>
+        <v>8.4616363636363641</v>
+      </c>
       <c r="AL44" s="1"/>
       <c r="AM44" s="1"/>
       <c r="AN44" s="1"/>
@@ -5604,7 +5714,7 @@
         <v>286</v>
       </c>
       <c r="L45" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-74</v>
       </c>
       <c r="M45" s="1"/>
@@ -5616,7 +5726,7 @@
       </c>
       <c r="R45" s="1"/>
       <c r="S45" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>42.4</v>
       </c>
       <c r="T45" s="5">
@@ -5626,13 +5736,13 @@
         <f t="shared" si="5"/>
         <v>50</v>
       </c>
-      <c r="V45" s="19"/>
+      <c r="V45" s="1"/>
       <c r="W45" s="1">
         <f t="shared" si="6"/>
         <v>4.9528301886792452</v>
       </c>
       <c r="X45" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3.7735849056603774</v>
       </c>
       <c r="Y45" s="1">
@@ -5670,7 +5780,10 @@
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
-      <c r="AK45" s="1"/>
+      <c r="AK45" s="1">
+        <f t="shared" si="8"/>
+        <v>35.236363636363635</v>
+      </c>
       <c r="AL45" s="1"/>
       <c r="AM45" s="1"/>
       <c r="AN45" s="1"/>
@@ -5709,7 +5822,7 @@
         <v>235</v>
       </c>
       <c r="L46" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-96</v>
       </c>
       <c r="M46" s="1"/>
@@ -5721,7 +5834,7 @@
       </c>
       <c r="R46" s="1"/>
       <c r="S46" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>27.8</v>
       </c>
       <c r="T46" s="5"/>
@@ -5729,13 +5842,13 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="V46" s="19"/>
+      <c r="V46" s="1"/>
       <c r="W46" s="1">
         <f t="shared" si="6"/>
         <v>12.62589928057554</v>
       </c>
       <c r="X46" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>12.62589928057554</v>
       </c>
       <c r="Y46" s="1">
@@ -5773,7 +5886,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AK46" s="1"/>
+      <c r="AK46" s="1">
+        <f t="shared" si="8"/>
+        <v>33.909090909090907</v>
+      </c>
       <c r="AL46" s="1"/>
       <c r="AM46" s="1"/>
       <c r="AN46" s="1"/>
@@ -5814,7 +5930,7 @@
         <v>98.75</v>
       </c>
       <c r="L47" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-15.590000000000003</v>
       </c>
       <c r="M47" s="1"/>
@@ -5826,7 +5942,7 @@
       </c>
       <c r="R47" s="1"/>
       <c r="S47" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>16.631999999999998</v>
       </c>
       <c r="T47" s="5"/>
@@ -5834,13 +5950,13 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="V47" s="19"/>
+      <c r="V47" s="1"/>
       <c r="W47" s="1">
         <f t="shared" si="6"/>
         <v>21.48003848003848</v>
       </c>
       <c r="X47" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>21.48003848003848</v>
       </c>
       <c r="Y47" s="1">
@@ -5880,7 +5996,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AK47" s="1"/>
+      <c r="AK47" s="1">
+        <f t="shared" si="8"/>
+        <v>23.55645454545455</v>
+      </c>
       <c r="AL47" s="1"/>
       <c r="AM47" s="1"/>
       <c r="AN47" s="1"/>
@@ -5921,7 +6040,7 @@
         <v>1332</v>
       </c>
       <c r="L48" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-25</v>
       </c>
       <c r="M48" s="1"/>
@@ -5933,7 +6052,7 @@
       </c>
       <c r="R48" s="1"/>
       <c r="S48" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>261.39999999999998</v>
       </c>
       <c r="T48" s="5"/>
@@ -5941,13 +6060,13 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="V48" s="19"/>
+      <c r="V48" s="1"/>
       <c r="W48" s="1">
         <f t="shared" si="6"/>
         <v>10.941086457536343</v>
       </c>
       <c r="X48" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>10.941086457536343</v>
       </c>
       <c r="Y48" s="1">
@@ -5985,7 +6104,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AK48" s="1"/>
+      <c r="AK48" s="1">
+        <f t="shared" si="8"/>
+        <v>287.63636363636363</v>
+      </c>
       <c r="AL48" s="1"/>
       <c r="AM48" s="1"/>
       <c r="AN48" s="1"/>
@@ -6026,7 +6148,7 @@
         <v>331</v>
       </c>
       <c r="L49" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-82</v>
       </c>
       <c r="M49" s="1"/>
@@ -6038,7 +6160,7 @@
       </c>
       <c r="R49" s="1"/>
       <c r="S49" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>49.8</v>
       </c>
       <c r="T49" s="5"/>
@@ -6046,13 +6168,13 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="V49" s="19"/>
+      <c r="V49" s="1"/>
       <c r="W49" s="1">
         <f t="shared" si="6"/>
         <v>30.562248995983939</v>
       </c>
       <c r="X49" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>30.562248995983939</v>
       </c>
       <c r="Y49" s="1">
@@ -6090,7 +6212,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AK49" s="1"/>
+      <c r="AK49" s="1">
+        <f t="shared" si="8"/>
+        <v>115.61818181818181</v>
+      </c>
       <c r="AL49" s="1"/>
       <c r="AM49" s="1"/>
       <c r="AN49" s="1"/>
@@ -6131,7 +6256,7 @@
         <v>491.53</v>
       </c>
       <c r="L50" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>17.380000000000052</v>
       </c>
       <c r="M50" s="1"/>
@@ -6143,24 +6268,24 @@
       </c>
       <c r="R50" s="1"/>
       <c r="S50" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>101.78200000000001</v>
       </c>
       <c r="T50" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>45.375512000000185</v>
       </c>
       <c r="U50" s="5">
         <f t="shared" si="5"/>
         <v>45.375512000000185</v>
       </c>
-      <c r="V50" s="19"/>
+      <c r="V50" s="1"/>
       <c r="W50" s="1">
         <f t="shared" si="6"/>
         <v>10.499999999999998</v>
       </c>
       <c r="X50" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>10.054189227957789</v>
       </c>
       <c r="Y50" s="1">
@@ -6198,7 +6323,10 @@
         <f t="shared" si="7"/>
         <v>45</v>
       </c>
-      <c r="AK50" s="1"/>
+      <c r="AK50" s="1">
+        <f t="shared" si="8"/>
+        <v>98.771090909090901</v>
+      </c>
       <c r="AL50" s="1"/>
       <c r="AM50" s="1"/>
       <c r="AN50" s="1"/>
@@ -6239,7 +6367,7 @@
         <v>515.32000000000005</v>
       </c>
       <c r="L51" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>19.342999999999961</v>
       </c>
       <c r="M51" s="1"/>
@@ -6253,7 +6381,7 @@
       </c>
       <c r="R51" s="1"/>
       <c r="S51" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>106.93260000000001</v>
       </c>
       <c r="T51" s="5"/>
@@ -6261,13 +6389,13 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="V51" s="19"/>
+      <c r="V51" s="1"/>
       <c r="W51" s="1">
         <f t="shared" si="6"/>
         <v>11.756225061393812</v>
       </c>
       <c r="X51" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>11.756225061393812</v>
       </c>
       <c r="Y51" s="1">
@@ -6305,7 +6433,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AK51" s="1"/>
+      <c r="AK51" s="1">
+        <f t="shared" si="8"/>
+        <v>114.04458181818183</v>
+      </c>
       <c r="AL51" s="1"/>
       <c r="AM51" s="1"/>
       <c r="AN51" s="1"/>
@@ -6346,7 +6477,7 @@
         <v>96.6</v>
       </c>
       <c r="L52" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>3.1310000000000002</v>
       </c>
       <c r="M52" s="1"/>
@@ -6358,24 +6489,24 @@
       </c>
       <c r="R52" s="1"/>
       <c r="S52" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>19.946199999999997</v>
       </c>
       <c r="T52" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>19.720699999999979</v>
       </c>
       <c r="U52" s="5">
         <f t="shared" si="5"/>
         <v>19.720699999999979</v>
       </c>
-      <c r="V52" s="19"/>
+      <c r="V52" s="1"/>
       <c r="W52" s="1">
         <f t="shared" si="6"/>
         <v>10.5</v>
       </c>
       <c r="X52" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>9.5113054115570907</v>
       </c>
       <c r="Y52" s="1">
@@ -6413,7 +6544,10 @@
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
-      <c r="AK52" s="1"/>
+      <c r="AK52" s="1">
+        <f t="shared" si="8"/>
+        <v>9.9446909090909106</v>
+      </c>
       <c r="AL52" s="1"/>
       <c r="AM52" s="1"/>
       <c r="AN52" s="1"/>
@@ -6452,7 +6586,7 @@
         <v>210</v>
       </c>
       <c r="L53" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-3</v>
       </c>
       <c r="M53" s="1"/>
@@ -6464,24 +6598,24 @@
       </c>
       <c r="R53" s="1"/>
       <c r="S53" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>41.4</v>
       </c>
       <c r="T53" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>5.6999999999999886</v>
       </c>
       <c r="U53" s="5">
         <f t="shared" si="5"/>
         <v>5.6999999999999886</v>
       </c>
-      <c r="V53" s="19"/>
+      <c r="V53" s="1"/>
       <c r="W53" s="1">
         <f t="shared" si="6"/>
         <v>10.5</v>
       </c>
       <c r="X53" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>10.362318840579711</v>
       </c>
       <c r="Y53" s="1">
@@ -6519,7 +6653,10 @@
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="AK53" s="1"/>
+      <c r="AK53" s="1">
+        <f t="shared" si="8"/>
+        <v>53.727272727272741</v>
+      </c>
       <c r="AL53" s="1"/>
       <c r="AM53" s="1"/>
       <c r="AN53" s="1"/>
@@ -6560,7 +6697,7 @@
         <v>469</v>
       </c>
       <c r="L54" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-11</v>
       </c>
       <c r="M54" s="1"/>
@@ -6574,7 +6711,7 @@
       </c>
       <c r="R54" s="1"/>
       <c r="S54" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>91.6</v>
       </c>
       <c r="T54" s="5"/>
@@ -6582,13 +6719,13 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="V54" s="19"/>
+      <c r="V54" s="1"/>
       <c r="W54" s="1">
         <f t="shared" si="6"/>
         <v>11.419213973799128</v>
       </c>
       <c r="X54" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>11.419213973799128</v>
       </c>
       <c r="Y54" s="1">
@@ -6626,7 +6763,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AK54" s="1"/>
+      <c r="AK54" s="1">
+        <f t="shared" si="8"/>
+        <v>102.18181818181819</v>
+      </c>
       <c r="AL54" s="1"/>
       <c r="AM54" s="1"/>
       <c r="AN54" s="1"/>
@@ -6667,7 +6807,7 @@
         <v>167</v>
       </c>
       <c r="L55" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-13</v>
       </c>
       <c r="M55" s="1"/>
@@ -6679,7 +6819,7 @@
       </c>
       <c r="R55" s="1"/>
       <c r="S55" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>30.8</v>
       </c>
       <c r="T55" s="5"/>
@@ -6687,13 +6827,13 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="V55" s="19"/>
+      <c r="V55" s="1"/>
       <c r="W55" s="1">
         <f t="shared" si="6"/>
         <v>10.7987012987013</v>
       </c>
       <c r="X55" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>10.7987012987013</v>
       </c>
       <c r="Y55" s="1">
@@ -6731,7 +6871,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AK55" s="1"/>
+      <c r="AK55" s="1">
+        <f t="shared" si="8"/>
+        <v>28.218181818181822</v>
+      </c>
       <c r="AL55" s="1"/>
       <c r="AM55" s="1"/>
       <c r="AN55" s="1"/>
@@ -6772,7 +6915,7 @@
         <v>88</v>
       </c>
       <c r="L56" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-2</v>
       </c>
       <c r="M56" s="1"/>
@@ -6784,7 +6927,7 @@
       </c>
       <c r="R56" s="1"/>
       <c r="S56" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>17.2</v>
       </c>
       <c r="T56" s="5">
@@ -6794,13 +6937,13 @@
         <f t="shared" si="5"/>
         <v>20</v>
       </c>
-      <c r="V56" s="19"/>
+      <c r="V56" s="1"/>
       <c r="W56" s="1">
         <f t="shared" si="6"/>
         <v>8.4186046511627914</v>
       </c>
       <c r="X56" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>7.2558139534883734</v>
       </c>
       <c r="Y56" s="1">
@@ -6838,7 +6981,10 @@
         <f t="shared" si="7"/>
         <v>8</v>
       </c>
-      <c r="AK56" s="1"/>
+      <c r="AK56" s="1">
+        <f t="shared" si="8"/>
+        <v>12.69090909090909</v>
+      </c>
       <c r="AL56" s="1"/>
       <c r="AM56" s="1"/>
       <c r="AN56" s="1"/>
@@ -6879,7 +7025,7 @@
         <v>693.53</v>
       </c>
       <c r="L57" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>16.576000000000022</v>
       </c>
       <c r="M57" s="1"/>
@@ -6893,7 +7039,7 @@
       </c>
       <c r="R57" s="1"/>
       <c r="S57" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>142.02119999999999</v>
       </c>
       <c r="T57" s="5"/>
@@ -6901,13 +7047,13 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="V57" s="19"/>
+      <c r="V57" s="1"/>
       <c r="W57" s="1">
         <f t="shared" si="6"/>
         <v>12.160299891847135</v>
       </c>
       <c r="X57" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>12.160299891847135</v>
       </c>
       <c r="Y57" s="1">
@@ -6945,7 +7091,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AK57" s="1"/>
+      <c r="AK57" s="1">
+        <f t="shared" si="8"/>
+        <v>146.36901818181818</v>
+      </c>
       <c r="AL57" s="1"/>
       <c r="AM57" s="1"/>
       <c r="AN57" s="1"/>
@@ -6982,7 +7131,7 @@
       </c>
       <c r="K58" s="11"/>
       <c r="L58" s="11">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M58" s="11"/>
@@ -6994,7 +7143,7 @@
       </c>
       <c r="R58" s="11"/>
       <c r="S58" s="11">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="T58" s="13"/>
@@ -7002,13 +7151,13 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="V58" s="20"/>
+      <c r="V58" s="11"/>
       <c r="W58" s="1" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X58" s="11" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y58" s="11">
@@ -7046,7 +7195,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AK58" s="1"/>
+      <c r="AK58" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="AL58" s="1"/>
       <c r="AM58" s="1"/>
       <c r="AN58" s="1"/>
@@ -7087,7 +7239,7 @@
         <v>282</v>
       </c>
       <c r="L59" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M59" s="1"/>
@@ -7099,24 +7251,24 @@
       </c>
       <c r="R59" s="1"/>
       <c r="S59" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>56.4</v>
       </c>
       <c r="T59" s="5">
-        <f t="shared" ref="T59:T84" si="15">10.5*S59-R59-Q59-P59-O59-F59</f>
+        <f t="shared" ref="T59:T84" si="16">10.5*S59-R59-Q59-P59-O59-F59</f>
         <v>169.60000000000002</v>
       </c>
       <c r="U59" s="5">
         <f t="shared" si="5"/>
         <v>169.60000000000002</v>
       </c>
-      <c r="V59" s="19"/>
+      <c r="V59" s="1"/>
       <c r="W59" s="1">
         <f t="shared" si="6"/>
         <v>10.499999999999998</v>
       </c>
       <c r="X59" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>7.492907801418438</v>
       </c>
       <c r="Y59" s="1">
@@ -7154,7 +7306,10 @@
         <f t="shared" si="7"/>
         <v>17</v>
       </c>
-      <c r="AK59" s="1"/>
+      <c r="AK59" s="1">
+        <f t="shared" si="8"/>
+        <v>37.090909090909086</v>
+      </c>
       <c r="AL59" s="1"/>
       <c r="AM59" s="1"/>
       <c r="AN59" s="1"/>
@@ -7195,7 +7350,7 @@
         <v>810.25</v>
       </c>
       <c r="L60" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>16.575000000000045</v>
       </c>
       <c r="M60" s="1"/>
@@ -7209,7 +7364,7 @@
       </c>
       <c r="R60" s="1"/>
       <c r="S60" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>165.36500000000001</v>
       </c>
       <c r="T60" s="5"/>
@@ -7217,13 +7372,13 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="V60" s="19"/>
+      <c r="V60" s="1"/>
       <c r="W60" s="1">
         <f t="shared" si="6"/>
         <v>11.017646049647748</v>
       </c>
       <c r="X60" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>11.017646049647748</v>
       </c>
       <c r="Y60" s="1">
@@ -7261,7 +7416,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AK60" s="1"/>
+      <c r="AK60" s="1">
+        <f t="shared" si="8"/>
+        <v>172.73734545454545</v>
+      </c>
       <c r="AL60" s="1"/>
       <c r="AM60" s="1"/>
       <c r="AN60" s="1"/>
@@ -7302,7 +7460,7 @@
         <v>85.05</v>
       </c>
       <c r="L61" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-1.9179999999999922</v>
       </c>
       <c r="M61" s="1"/>
@@ -7314,7 +7472,7 @@
       </c>
       <c r="R61" s="1"/>
       <c r="S61" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>16.6264</v>
       </c>
       <c r="T61" s="5"/>
@@ -7322,13 +7480,13 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="V61" s="19"/>
+      <c r="V61" s="1"/>
       <c r="W61" s="1">
         <f t="shared" si="6"/>
         <v>12.785115478997259</v>
       </c>
       <c r="X61" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>12.785115478997259</v>
       </c>
       <c r="Y61" s="1">
@@ -7366,7 +7524,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AK61" s="1"/>
+      <c r="AK61" s="1">
+        <f t="shared" si="8"/>
+        <v>19.781418181818182</v>
+      </c>
       <c r="AL61" s="1"/>
       <c r="AM61" s="1"/>
       <c r="AN61" s="1"/>
@@ -7407,7 +7568,7 @@
         <v>189</v>
       </c>
       <c r="L62" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-1</v>
       </c>
       <c r="M62" s="1"/>
@@ -7419,24 +7580,24 @@
       </c>
       <c r="R62" s="1"/>
       <c r="S62" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>37.6</v>
       </c>
       <c r="T62" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>63.400000000000034</v>
       </c>
       <c r="U62" s="5">
         <f t="shared" si="5"/>
         <v>63.400000000000034</v>
       </c>
-      <c r="V62" s="19"/>
+      <c r="V62" s="1"/>
       <c r="W62" s="1">
         <f t="shared" si="6"/>
         <v>10.5</v>
       </c>
       <c r="X62" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>8.8138297872340416</v>
       </c>
       <c r="Y62" s="1">
@@ -7474,7 +7635,10 @@
         <f t="shared" si="7"/>
         <v>6</v>
       </c>
-      <c r="AK62" s="1"/>
+      <c r="AK62" s="1">
+        <f t="shared" si="8"/>
+        <v>32.981818181818191</v>
+      </c>
       <c r="AL62" s="1"/>
       <c r="AM62" s="1"/>
       <c r="AN62" s="1"/>
@@ -7515,7 +7679,7 @@
         <v>273</v>
       </c>
       <c r="L63" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-12</v>
       </c>
       <c r="M63" s="1"/>
@@ -7527,24 +7691,24 @@
       </c>
       <c r="R63" s="1"/>
       <c r="S63" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>52.2</v>
       </c>
       <c r="T63" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>131.10000000000002</v>
       </c>
       <c r="U63" s="5">
         <f t="shared" si="5"/>
         <v>131.10000000000002</v>
       </c>
-      <c r="V63" s="19"/>
+      <c r="V63" s="1"/>
       <c r="W63" s="1">
         <f t="shared" si="6"/>
         <v>10.5</v>
       </c>
       <c r="X63" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>7.9885057471264362</v>
       </c>
       <c r="Y63" s="1">
@@ -7582,7 +7746,10 @@
         <f t="shared" si="7"/>
         <v>52</v>
       </c>
-      <c r="AK63" s="1"/>
+      <c r="AK63" s="1">
+        <f t="shared" si="8"/>
+        <v>47.745454545454542</v>
+      </c>
       <c r="AL63" s="1"/>
       <c r="AM63" s="1"/>
       <c r="AN63" s="1"/>
@@ -7623,7 +7790,7 @@
         <v>116.7</v>
       </c>
       <c r="L64" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-14.328000000000003</v>
       </c>
       <c r="M64" s="1"/>
@@ -7635,24 +7802,24 @@
       </c>
       <c r="R64" s="1"/>
       <c r="S64" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>20.474399999999999</v>
       </c>
       <c r="T64" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>73.716200000000001</v>
       </c>
       <c r="U64" s="5">
         <f t="shared" si="5"/>
         <v>73.716200000000001</v>
       </c>
-      <c r="V64" s="19"/>
+      <c r="V64" s="1"/>
       <c r="W64" s="1">
         <f t="shared" si="6"/>
         <v>10.5</v>
       </c>
       <c r="X64" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>6.8995916852264285</v>
       </c>
       <c r="Y64" s="1">
@@ -7692,7 +7859,10 @@
         <f t="shared" si="7"/>
         <v>74</v>
       </c>
-      <c r="AK64" s="1"/>
+      <c r="AK64" s="1">
+        <f t="shared" si="8"/>
+        <v>9.9568909090909088</v>
+      </c>
       <c r="AL64" s="1"/>
       <c r="AM64" s="1"/>
       <c r="AN64" s="1"/>
@@ -7729,7 +7899,7 @@
         <v>1.3</v>
       </c>
       <c r="L65" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-1.3</v>
       </c>
       <c r="M65" s="1"/>
@@ -7741,7 +7911,7 @@
       </c>
       <c r="R65" s="1"/>
       <c r="S65" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="T65" s="5"/>
@@ -7749,13 +7919,13 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="V65" s="19"/>
+      <c r="V65" s="1"/>
       <c r="W65" s="1" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X65" s="1" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y65" s="1">
@@ -7795,7 +7965,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AK65" s="1"/>
+      <c r="AK65" s="1">
+        <f t="shared" si="8"/>
+        <v>7.4163636363636362E-2</v>
+      </c>
       <c r="AL65" s="1"/>
       <c r="AM65" s="1"/>
       <c r="AN65" s="1"/>
@@ -7836,7 +8009,7 @@
         <v>955</v>
       </c>
       <c r="L66" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-24</v>
       </c>
       <c r="M66" s="1"/>
@@ -7850,24 +8023,24 @@
       </c>
       <c r="R66" s="1"/>
       <c r="S66" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>186.2</v>
       </c>
       <c r="T66" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>182.952</v>
       </c>
       <c r="U66" s="5">
         <f t="shared" si="5"/>
         <v>182.952</v>
       </c>
-      <c r="V66" s="19"/>
+      <c r="V66" s="1"/>
       <c r="W66" s="1">
         <f t="shared" si="6"/>
         <v>10.5</v>
       </c>
       <c r="X66" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>9.5174436090225569</v>
       </c>
       <c r="Y66" s="1">
@@ -7905,7 +8078,10 @@
         <f t="shared" si="7"/>
         <v>73</v>
       </c>
-      <c r="AK66" s="1"/>
+      <c r="AK66" s="1">
+        <f t="shared" si="8"/>
+        <v>163.69090909090909</v>
+      </c>
       <c r="AL66" s="1"/>
       <c r="AM66" s="1"/>
       <c r="AN66" s="1"/>
@@ -7944,7 +8120,7 @@
         <v>657</v>
       </c>
       <c r="L67" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-652</v>
       </c>
       <c r="M67" s="1"/>
@@ -7958,7 +8134,7 @@
       </c>
       <c r="R67" s="1"/>
       <c r="S67" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="T67" s="5">
@@ -7968,13 +8144,13 @@
         <f t="shared" si="5"/>
         <v>300</v>
       </c>
-      <c r="V67" s="19"/>
+      <c r="V67" s="1"/>
       <c r="W67" s="1">
         <f t="shared" si="6"/>
         <v>606</v>
       </c>
       <c r="X67" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>306</v>
       </c>
       <c r="Y67" s="1">
@@ -8012,7 +8188,10 @@
         <f t="shared" si="7"/>
         <v>120</v>
       </c>
-      <c r="AK67" s="1"/>
+      <c r="AK67" s="1">
+        <f t="shared" si="8"/>
+        <v>104.23636363636365</v>
+      </c>
       <c r="AL67" s="1"/>
       <c r="AM67" s="1"/>
       <c r="AN67" s="1"/>
@@ -8053,7 +8232,7 @@
         <v>267.10000000000002</v>
       </c>
       <c r="L68" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>8.6159999999999854</v>
       </c>
       <c r="M68" s="1"/>
@@ -8065,24 +8244,24 @@
       </c>
       <c r="R68" s="1"/>
       <c r="S68" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>55.1432</v>
       </c>
       <c r="T68" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>75.094666000000075</v>
       </c>
       <c r="U68" s="5">
         <f t="shared" si="5"/>
         <v>75.094666000000075</v>
       </c>
-      <c r="V68" s="19"/>
+      <c r="V68" s="1"/>
       <c r="W68" s="1">
         <f t="shared" si="6"/>
         <v>10.5</v>
       </c>
       <c r="X68" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>9.1381880993486035</v>
       </c>
       <c r="Y68" s="1">
@@ -8120,7 +8299,10 @@
         <f t="shared" si="7"/>
         <v>75</v>
       </c>
-      <c r="AK68" s="1"/>
+      <c r="AK68" s="1">
+        <f t="shared" si="8"/>
+        <v>57.340545454545456</v>
+      </c>
       <c r="AL68" s="1"/>
       <c r="AM68" s="1"/>
       <c r="AN68" s="1"/>
@@ -8161,7 +8343,7 @@
         <v>432.6</v>
       </c>
       <c r="L69" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>6.117999999999995</v>
       </c>
       <c r="M69" s="1"/>
@@ -8173,24 +8355,24 @@
       </c>
       <c r="R69" s="1"/>
       <c r="S69" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>87.743600000000001</v>
       </c>
       <c r="T69" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>197.86857199999992</v>
       </c>
       <c r="U69" s="5">
         <f t="shared" si="5"/>
         <v>197.86857199999992</v>
       </c>
-      <c r="V69" s="19"/>
+      <c r="V69" s="1"/>
       <c r="W69" s="1">
         <f t="shared" si="6"/>
         <v>10.5</v>
       </c>
       <c r="X69" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>8.2449230257249546</v>
       </c>
       <c r="Y69" s="1">
@@ -8228,7 +8410,10 @@
         <f t="shared" si="7"/>
         <v>198</v>
       </c>
-      <c r="AK69" s="1"/>
+      <c r="AK69" s="1">
+        <f t="shared" si="8"/>
+        <v>67.759490909090914</v>
+      </c>
       <c r="AL69" s="1"/>
       <c r="AM69" s="1"/>
       <c r="AN69" s="1"/>
@@ -8269,7 +8454,7 @@
         <v>659.55</v>
       </c>
       <c r="L70" s="1">
-        <f t="shared" ref="L70:L101" si="16">E70-K70</f>
+        <f t="shared" ref="L70:L101" si="17">E70-K70</f>
         <v>26.824000000000069</v>
       </c>
       <c r="M70" s="1"/>
@@ -8283,7 +8468,7 @@
       </c>
       <c r="R70" s="1"/>
       <c r="S70" s="1">
-        <f t="shared" ref="S70:S101" si="17">E70/5</f>
+        <f t="shared" ref="S70:S101" si="18">E70/5</f>
         <v>137.2748</v>
       </c>
       <c r="T70" s="5"/>
@@ -8291,13 +8476,13 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="V70" s="19"/>
+      <c r="V70" s="1"/>
       <c r="W70" s="1">
         <f t="shared" si="6"/>
         <v>15.542354088295889</v>
       </c>
       <c r="X70" s="1">
-        <f t="shared" ref="X70:X101" si="18">(F70+O70+P70+Q70+R70)/S70</f>
+        <f t="shared" ref="X70:X101" si="19">(F70+O70+P70+Q70+R70)/S70</f>
         <v>15.542354088295889</v>
       </c>
       <c r="Y70" s="1">
@@ -8335,7 +8520,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AK70" s="1"/>
+      <c r="AK70" s="1">
+        <f t="shared" si="8"/>
+        <v>167.52110909090908</v>
+      </c>
       <c r="AL70" s="1"/>
       <c r="AM70" s="1"/>
       <c r="AN70" s="1"/>
@@ -8376,7 +8564,7 @@
         <v>228.45</v>
       </c>
       <c r="L71" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-6.5229999999999961</v>
       </c>
       <c r="M71" s="1"/>
@@ -8388,24 +8576,24 @@
       </c>
       <c r="R71" s="1"/>
       <c r="S71" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>44.385399999999997</v>
       </c>
       <c r="T71" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>19.839700000000107</v>
       </c>
       <c r="U71" s="5">
-        <f t="shared" ref="U71:U134" si="19">T71</f>
+        <f t="shared" ref="U71:U134" si="20">T71</f>
         <v>19.839700000000107</v>
       </c>
-      <c r="V71" s="19"/>
+      <c r="V71" s="1"/>
       <c r="W71" s="1">
-        <f t="shared" ref="W71:W134" si="20">(F71+O71+P71+Q71+R71+U71)/S71</f>
+        <f t="shared" ref="W71:W134" si="21">(F71+O71+P71+Q71+R71+U71)/S71</f>
         <v>10.5</v>
       </c>
       <c r="X71" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>10.053012927674413</v>
       </c>
       <c r="Y71" s="1">
@@ -8440,10 +8628,13 @@
       </c>
       <c r="AI71" s="1"/>
       <c r="AJ71" s="1">
-        <f t="shared" ref="AJ71:AJ134" si="21">ROUND(G71*U71,0)</f>
+        <f t="shared" ref="AJ71:AJ134" si="22">ROUND(G71*U71,0)</f>
         <v>20</v>
       </c>
-      <c r="AK71" s="1"/>
+      <c r="AK71" s="1">
+        <f t="shared" ref="AK71:AK134" si="23">(SUM(Y71:AH71)+S71)/11</f>
+        <v>49.726290909090899</v>
+      </c>
       <c r="AL71" s="1"/>
       <c r="AM71" s="1"/>
       <c r="AN71" s="1"/>
@@ -8484,7 +8675,7 @@
         <v>10</v>
       </c>
       <c r="L72" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-8</v>
       </c>
       <c r="M72" s="1"/>
@@ -8496,21 +8687,21 @@
       </c>
       <c r="R72" s="1"/>
       <c r="S72" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.4</v>
       </c>
       <c r="T72" s="5"/>
       <c r="U72" s="5">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="V72" s="1"/>
+      <c r="W72" s="1">
+        <f t="shared" si="21"/>
+        <v>60</v>
+      </c>
+      <c r="X72" s="1">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V72" s="19"/>
-      <c r="W72" s="1">
-        <f t="shared" si="20"/>
-        <v>60</v>
-      </c>
-      <c r="X72" s="1">
-        <f t="shared" si="18"/>
         <v>60</v>
       </c>
       <c r="Y72" s="1">
@@ -8545,10 +8736,13 @@
       </c>
       <c r="AI72" s="1"/>
       <c r="AJ72" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AK72" s="1"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AK72" s="1">
+        <f t="shared" si="23"/>
+        <v>1.3090909090909091</v>
+      </c>
       <c r="AL72" s="1"/>
       <c r="AM72" s="1"/>
       <c r="AN72" s="1"/>
@@ -8589,7 +8783,7 @@
         <v>338.58</v>
       </c>
       <c r="L73" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-37.557999999999993</v>
       </c>
       <c r="M73" s="1"/>
@@ -8601,21 +8795,21 @@
       </c>
       <c r="R73" s="1"/>
       <c r="S73" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>60.2044</v>
       </c>
       <c r="T73" s="5"/>
       <c r="U73" s="5">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="V73" s="1"/>
+      <c r="W73" s="1">
+        <f t="shared" si="21"/>
+        <v>15.775174738059018</v>
+      </c>
+      <c r="X73" s="1">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V73" s="19"/>
-      <c r="W73" s="1">
-        <f t="shared" si="20"/>
-        <v>15.775174738059018</v>
-      </c>
-      <c r="X73" s="1">
-        <f t="shared" si="18"/>
         <v>15.775174738059018</v>
       </c>
       <c r="Y73" s="1">
@@ -8650,10 +8844,13 @@
       </c>
       <c r="AI73" s="1"/>
       <c r="AJ73" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AK73" s="1"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AK73" s="1">
+        <f t="shared" si="23"/>
+        <v>69.376763636363634</v>
+      </c>
       <c r="AL73" s="1"/>
       <c r="AM73" s="1"/>
       <c r="AN73" s="1"/>
@@ -8694,7 +8891,7 @@
         <v>133</v>
       </c>
       <c r="L74" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-6</v>
       </c>
       <c r="M74" s="1"/>
@@ -8706,24 +8903,24 @@
       </c>
       <c r="R74" s="1"/>
       <c r="S74" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>25.4</v>
       </c>
       <c r="T74" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>28.699999999999989</v>
       </c>
       <c r="U74" s="5">
+        <f t="shared" si="20"/>
+        <v>28.699999999999989</v>
+      </c>
+      <c r="V74" s="1"/>
+      <c r="W74" s="1">
+        <f t="shared" si="21"/>
+        <v>10.5</v>
+      </c>
+      <c r="X74" s="1">
         <f t="shared" si="19"/>
-        <v>28.699999999999989</v>
-      </c>
-      <c r="V74" s="19"/>
-      <c r="W74" s="1">
-        <f t="shared" si="20"/>
-        <v>10.5</v>
-      </c>
-      <c r="X74" s="1">
-        <f t="shared" si="18"/>
         <v>9.3700787401574814</v>
       </c>
       <c r="Y74" s="1">
@@ -8758,10 +8955,13 @@
       </c>
       <c r="AI74" s="1"/>
       <c r="AJ74" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>17</v>
       </c>
-      <c r="AK74" s="1"/>
+      <c r="AK74" s="1">
+        <f t="shared" si="23"/>
+        <v>22.054545454545455</v>
+      </c>
       <c r="AL74" s="1"/>
       <c r="AM74" s="1"/>
       <c r="AN74" s="1"/>
@@ -8802,7 +9002,7 @@
         <v>22</v>
       </c>
       <c r="L75" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M75" s="1"/>
@@ -8814,21 +9014,21 @@
       </c>
       <c r="R75" s="1"/>
       <c r="S75" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>4.4000000000000004</v>
       </c>
       <c r="T75" s="5"/>
       <c r="U75" s="5">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="V75" s="1"/>
+      <c r="W75" s="1">
+        <f t="shared" si="21"/>
+        <v>15.454545454545453</v>
+      </c>
+      <c r="X75" s="1">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V75" s="19"/>
-      <c r="W75" s="1">
-        <f t="shared" si="20"/>
-        <v>15.454545454545453</v>
-      </c>
-      <c r="X75" s="1">
-        <f t="shared" si="18"/>
         <v>15.454545454545453</v>
       </c>
       <c r="Y75" s="1">
@@ -8863,10 +9063,13 @@
       </c>
       <c r="AI75" s="1"/>
       <c r="AJ75" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AK75" s="1"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AK75" s="1">
+        <f t="shared" si="23"/>
+        <v>5.4363636363636365</v>
+      </c>
       <c r="AL75" s="1"/>
       <c r="AM75" s="1"/>
       <c r="AN75" s="1"/>
@@ -8907,7 +9110,7 @@
         <v>112</v>
       </c>
       <c r="L76" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-1</v>
       </c>
       <c r="M76" s="1"/>
@@ -8919,24 +9122,24 @@
       </c>
       <c r="R76" s="1"/>
       <c r="S76" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>22.2</v>
       </c>
       <c r="T76" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>54.499999999999972</v>
       </c>
       <c r="U76" s="5">
+        <f t="shared" si="20"/>
+        <v>54.499999999999972</v>
+      </c>
+      <c r="V76" s="1"/>
+      <c r="W76" s="1">
+        <f t="shared" si="21"/>
+        <v>10.5</v>
+      </c>
+      <c r="X76" s="1">
         <f t="shared" si="19"/>
-        <v>54.499999999999972</v>
-      </c>
-      <c r="V76" s="19"/>
-      <c r="W76" s="1">
-        <f t="shared" si="20"/>
-        <v>10.5</v>
-      </c>
-      <c r="X76" s="1">
-        <f t="shared" si="18"/>
         <v>8.0450450450450468</v>
       </c>
       <c r="Y76" s="1">
@@ -8971,10 +9174,13 @@
       </c>
       <c r="AI76" s="1"/>
       <c r="AJ76" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>22</v>
       </c>
-      <c r="AK76" s="1"/>
+      <c r="AK76" s="1">
+        <f t="shared" si="23"/>
+        <v>20.145454545454548</v>
+      </c>
       <c r="AL76" s="1"/>
       <c r="AM76" s="1"/>
       <c r="AN76" s="1"/>
@@ -9015,7 +9221,7 @@
         <v>144</v>
       </c>
       <c r="L77" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-1</v>
       </c>
       <c r="M77" s="1"/>
@@ -9027,24 +9233,24 @@
       </c>
       <c r="R77" s="1"/>
       <c r="S77" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>28.6</v>
       </c>
       <c r="T77" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>85.300000000000011</v>
       </c>
       <c r="U77" s="5">
+        <f t="shared" si="20"/>
+        <v>85.300000000000011</v>
+      </c>
+      <c r="V77" s="1"/>
+      <c r="W77" s="1">
+        <f t="shared" si="21"/>
+        <v>10.5</v>
+      </c>
+      <c r="X77" s="1">
         <f t="shared" si="19"/>
-        <v>85.300000000000011</v>
-      </c>
-      <c r="V77" s="19"/>
-      <c r="W77" s="1">
-        <f t="shared" si="20"/>
-        <v>10.5</v>
-      </c>
-      <c r="X77" s="1">
-        <f t="shared" si="18"/>
         <v>7.5174825174825175</v>
       </c>
       <c r="Y77" s="1">
@@ -9079,10 +9285,13 @@
       </c>
       <c r="AI77" s="1"/>
       <c r="AJ77" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>28</v>
       </c>
-      <c r="AK77" s="1"/>
+      <c r="AK77" s="1">
+        <f t="shared" si="23"/>
+        <v>24.490909090909089</v>
+      </c>
       <c r="AL77" s="1"/>
       <c r="AM77" s="1"/>
       <c r="AN77" s="1"/>
@@ -9123,7 +9332,7 @@
         <v>117</v>
       </c>
       <c r="L78" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-2</v>
       </c>
       <c r="M78" s="1"/>
@@ -9135,24 +9344,24 @@
       </c>
       <c r="R78" s="1"/>
       <c r="S78" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>23</v>
       </c>
       <c r="T78" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>61.5</v>
       </c>
       <c r="U78" s="5">
+        <f t="shared" si="20"/>
+        <v>61.5</v>
+      </c>
+      <c r="V78" s="1"/>
+      <c r="W78" s="1">
+        <f t="shared" si="21"/>
+        <v>10.5</v>
+      </c>
+      <c r="X78" s="1">
         <f t="shared" si="19"/>
-        <v>61.5</v>
-      </c>
-      <c r="V78" s="19"/>
-      <c r="W78" s="1">
-        <f t="shared" si="20"/>
-        <v>10.5</v>
-      </c>
-      <c r="X78" s="1">
-        <f t="shared" si="18"/>
         <v>7.8260869565217392</v>
       </c>
       <c r="Y78" s="1">
@@ -9187,10 +9396,13 @@
       </c>
       <c r="AI78" s="1"/>
       <c r="AJ78" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>22</v>
       </c>
-      <c r="AK78" s="1"/>
+      <c r="AK78" s="1">
+        <f t="shared" si="23"/>
+        <v>15.6</v>
+      </c>
       <c r="AL78" s="1"/>
       <c r="AM78" s="1"/>
       <c r="AN78" s="1"/>
@@ -9231,7 +9443,7 @@
         <v>408</v>
       </c>
       <c r="L79" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-12</v>
       </c>
       <c r="M79" s="1"/>
@@ -9243,21 +9455,21 @@
       </c>
       <c r="R79" s="1"/>
       <c r="S79" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>79.2</v>
       </c>
       <c r="T79" s="5"/>
       <c r="U79" s="5">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="V79" s="1"/>
+      <c r="W79" s="1">
+        <f t="shared" si="21"/>
+        <v>11.243472222222223</v>
+      </c>
+      <c r="X79" s="1">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V79" s="19"/>
-      <c r="W79" s="1">
-        <f t="shared" si="20"/>
-        <v>11.243472222222223</v>
-      </c>
-      <c r="X79" s="1">
-        <f t="shared" si="18"/>
         <v>11.243472222222223</v>
       </c>
       <c r="Y79" s="1">
@@ -9292,10 +9504,13 @@
       </c>
       <c r="AI79" s="1"/>
       <c r="AJ79" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AK79" s="1"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AK79" s="1">
+        <f t="shared" si="23"/>
+        <v>98.163636363636357</v>
+      </c>
       <c r="AL79" s="1"/>
       <c r="AM79" s="1"/>
       <c r="AN79" s="1"/>
@@ -9336,7 +9551,7 @@
         <v>76</v>
       </c>
       <c r="L80" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M80" s="1"/>
@@ -9348,21 +9563,21 @@
       </c>
       <c r="R80" s="1"/>
       <c r="S80" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>15.2</v>
       </c>
       <c r="T80" s="5"/>
       <c r="U80" s="5">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="V80" s="1"/>
+      <c r="W80" s="1">
+        <f t="shared" si="21"/>
+        <v>13.486842105263166</v>
+      </c>
+      <c r="X80" s="1">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V80" s="19"/>
-      <c r="W80" s="1">
-        <f t="shared" si="20"/>
-        <v>13.486842105263166</v>
-      </c>
-      <c r="X80" s="1">
-        <f t="shared" si="18"/>
         <v>13.486842105263166</v>
       </c>
       <c r="Y80" s="1">
@@ -9397,10 +9612,13 @@
       </c>
       <c r="AI80" s="1"/>
       <c r="AJ80" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AK80" s="1"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AK80" s="1">
+        <f t="shared" si="23"/>
+        <v>21.27272727272727</v>
+      </c>
       <c r="AL80" s="1"/>
       <c r="AM80" s="1"/>
       <c r="AN80" s="1"/>
@@ -9441,7 +9659,7 @@
         <v>55</v>
       </c>
       <c r="L81" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-2</v>
       </c>
       <c r="M81" s="1"/>
@@ -9453,24 +9671,24 @@
       </c>
       <c r="R81" s="1"/>
       <c r="S81" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>10.6</v>
       </c>
       <c r="T81" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>6.4999999999999858</v>
       </c>
       <c r="U81" s="5">
+        <f t="shared" si="20"/>
+        <v>6.4999999999999858</v>
+      </c>
+      <c r="V81" s="1"/>
+      <c r="W81" s="1">
+        <f t="shared" si="21"/>
+        <v>10.5</v>
+      </c>
+      <c r="X81" s="1">
         <f t="shared" si="19"/>
-        <v>6.4999999999999858</v>
-      </c>
-      <c r="V81" s="19"/>
-      <c r="W81" s="1">
-        <f t="shared" si="20"/>
-        <v>10.5</v>
-      </c>
-      <c r="X81" s="1">
-        <f t="shared" si="18"/>
         <v>9.8867924528301909</v>
       </c>
       <c r="Y81" s="1">
@@ -9505,10 +9723,13 @@
       </c>
       <c r="AI81" s="1"/>
       <c r="AJ81" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>2</v>
       </c>
-      <c r="AK81" s="1"/>
+      <c r="AK81" s="1">
+        <f t="shared" si="23"/>
+        <v>7.4727272727272718</v>
+      </c>
       <c r="AL81" s="1"/>
       <c r="AM81" s="1"/>
       <c r="AN81" s="1"/>
@@ -9549,7 +9770,7 @@
         <v>222</v>
       </c>
       <c r="L82" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-12</v>
       </c>
       <c r="M82" s="1"/>
@@ -9561,21 +9782,21 @@
       </c>
       <c r="R82" s="1"/>
       <c r="S82" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>42</v>
       </c>
       <c r="T82" s="5"/>
       <c r="U82" s="5">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="V82" s="1"/>
+      <c r="W82" s="1">
+        <f t="shared" si="21"/>
+        <v>10.939857142857148</v>
+      </c>
+      <c r="X82" s="1">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V82" s="19"/>
-      <c r="W82" s="1">
-        <f t="shared" si="20"/>
-        <v>10.939857142857148</v>
-      </c>
-      <c r="X82" s="1">
-        <f t="shared" si="18"/>
         <v>10.939857142857148</v>
       </c>
       <c r="Y82" s="1">
@@ -9610,10 +9831,13 @@
       </c>
       <c r="AI82" s="1"/>
       <c r="AJ82" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AK82" s="1"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AK82" s="1">
+        <f t="shared" si="23"/>
+        <v>51.018181818181823</v>
+      </c>
       <c r="AL82" s="1"/>
       <c r="AM82" s="1"/>
       <c r="AN82" s="1"/>
@@ -9654,7 +9878,7 @@
         <v>186</v>
       </c>
       <c r="L83" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-150</v>
       </c>
       <c r="M83" s="1"/>
@@ -9666,21 +9890,21 @@
       </c>
       <c r="R83" s="1"/>
       <c r="S83" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>7.2</v>
       </c>
       <c r="T83" s="5"/>
       <c r="U83" s="5">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="V83" s="1"/>
+      <c r="W83" s="1">
+        <f t="shared" si="21"/>
+        <v>25.305555555555554</v>
+      </c>
+      <c r="X83" s="1">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V83" s="19"/>
-      <c r="W83" s="1">
-        <f t="shared" si="20"/>
-        <v>25.305555555555554</v>
-      </c>
-      <c r="X83" s="1">
-        <f t="shared" si="18"/>
         <v>25.305555555555554</v>
       </c>
       <c r="Y83" s="1">
@@ -9715,10 +9939,13 @@
       </c>
       <c r="AI83" s="1"/>
       <c r="AJ83" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AK83" s="1"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AK83" s="1">
+        <f t="shared" si="23"/>
+        <v>16.945454545454542</v>
+      </c>
       <c r="AL83" s="1"/>
       <c r="AM83" s="1"/>
       <c r="AN83" s="1"/>
@@ -9759,7 +9986,7 @@
         <v>486</v>
       </c>
       <c r="L84" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-219</v>
       </c>
       <c r="M84" s="1"/>
@@ -9771,24 +9998,24 @@
       </c>
       <c r="R84" s="1"/>
       <c r="S84" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>53.4</v>
       </c>
       <c r="T84" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>50.89999999999992</v>
       </c>
       <c r="U84" s="5">
+        <f t="shared" si="20"/>
+        <v>50.89999999999992</v>
+      </c>
+      <c r="V84" s="1"/>
+      <c r="W84" s="1">
+        <f t="shared" si="21"/>
+        <v>10.499999999999998</v>
+      </c>
+      <c r="X84" s="1">
         <f t="shared" si="19"/>
-        <v>50.89999999999992</v>
-      </c>
-      <c r="V84" s="19"/>
-      <c r="W84" s="1">
-        <f t="shared" si="20"/>
-        <v>10.499999999999998</v>
-      </c>
-      <c r="X84" s="1">
-        <f t="shared" si="18"/>
         <v>9.54681647940075</v>
       </c>
       <c r="Y84" s="1">
@@ -9823,10 +10050,13 @@
       </c>
       <c r="AI84" s="1"/>
       <c r="AJ84" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>18</v>
       </c>
-      <c r="AK84" s="1"/>
+      <c r="AK84" s="1">
+        <f t="shared" si="23"/>
+        <v>48.345454545454544</v>
+      </c>
       <c r="AL84" s="1"/>
       <c r="AM84" s="1"/>
       <c r="AN84" s="1"/>
@@ -9865,7 +10095,7 @@
         <v>199</v>
       </c>
       <c r="L85" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M85" s="1"/>
@@ -9877,7 +10107,7 @@
       </c>
       <c r="R85" s="1"/>
       <c r="S85" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>39.799999999999997</v>
       </c>
       <c r="T85" s="5">
@@ -9885,16 +10115,16 @@
         <v>246.39999999999998</v>
       </c>
       <c r="U85" s="5">
+        <f t="shared" si="20"/>
+        <v>246.39999999999998</v>
+      </c>
+      <c r="V85" s="1"/>
+      <c r="W85" s="1">
+        <f t="shared" si="21"/>
+        <v>8</v>
+      </c>
+      <c r="X85" s="1">
         <f t="shared" si="19"/>
-        <v>246.39999999999998</v>
-      </c>
-      <c r="V85" s="19"/>
-      <c r="W85" s="1">
-        <f t="shared" si="20"/>
-        <v>8</v>
-      </c>
-      <c r="X85" s="1">
-        <f t="shared" si="18"/>
         <v>1.8090452261306533</v>
       </c>
       <c r="Y85" s="1">
@@ -9929,10 +10159,13 @@
       </c>
       <c r="AI85" s="1"/>
       <c r="AJ85" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>99</v>
       </c>
-      <c r="AK85" s="1"/>
+      <c r="AK85" s="1">
+        <f t="shared" si="23"/>
+        <v>20.418181818181814</v>
+      </c>
       <c r="AL85" s="1"/>
       <c r="AM85" s="1"/>
       <c r="AN85" s="1"/>
@@ -9973,7 +10206,7 @@
         <v>30.1</v>
       </c>
       <c r="L86" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.97799999999999798</v>
       </c>
       <c r="M86" s="1"/>
@@ -9985,21 +10218,21 @@
       </c>
       <c r="R86" s="1"/>
       <c r="S86" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>6.2156000000000002</v>
       </c>
       <c r="T86" s="5"/>
       <c r="U86" s="5">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="V86" s="1"/>
+      <c r="W86" s="1">
+        <f t="shared" si="21"/>
+        <v>14.764978441341141</v>
+      </c>
+      <c r="X86" s="1">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V86" s="19"/>
-      <c r="W86" s="1">
-        <f t="shared" si="20"/>
-        <v>14.764978441341141</v>
-      </c>
-      <c r="X86" s="1">
-        <f t="shared" si="18"/>
         <v>14.764978441341141</v>
       </c>
       <c r="Y86" s="1">
@@ -10034,10 +10267,13 @@
       </c>
       <c r="AI86" s="1"/>
       <c r="AJ86" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AK86" s="1"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AK86" s="1">
+        <f t="shared" si="23"/>
+        <v>7.5574727272727271</v>
+      </c>
       <c r="AL86" s="1"/>
       <c r="AM86" s="1"/>
       <c r="AN86" s="1"/>
@@ -10076,7 +10312,7 @@
         <v>28</v>
       </c>
       <c r="L87" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-8</v>
       </c>
       <c r="M87" s="11"/>
@@ -10088,21 +10324,21 @@
       </c>
       <c r="R87" s="11"/>
       <c r="S87" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>4</v>
       </c>
       <c r="T87" s="13"/>
       <c r="U87" s="5">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="V87" s="11"/>
+      <c r="W87" s="1">
+        <f t="shared" si="21"/>
+        <v>1.75</v>
+      </c>
+      <c r="X87" s="11">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V87" s="20"/>
-      <c r="W87" s="1">
-        <f t="shared" si="20"/>
-        <v>1.75</v>
-      </c>
-      <c r="X87" s="11">
-        <f t="shared" si="18"/>
         <v>1.75</v>
       </c>
       <c r="Y87" s="11">
@@ -10137,10 +10373,13 @@
       </c>
       <c r="AI87" s="11"/>
       <c r="AJ87" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AK87" s="1"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AK87" s="1">
+        <f t="shared" si="23"/>
+        <v>3.4181818181818184</v>
+      </c>
       <c r="AL87" s="1"/>
       <c r="AM87" s="1"/>
       <c r="AN87" s="1"/>
@@ -10179,7 +10418,7 @@
         <v>194.27</v>
       </c>
       <c r="L88" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>9.1399999999999864</v>
       </c>
       <c r="M88" s="1"/>
@@ -10191,24 +10430,24 @@
       </c>
       <c r="R88" s="1"/>
       <c r="S88" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>40.682000000000002</v>
       </c>
       <c r="T88" s="5">
-        <f t="shared" ref="T88" si="22">10.5*S88-R88-Q88-P88-O88-F88</f>
+        <f t="shared" ref="T88" si="24">10.5*S88-R88-Q88-P88-O88-F88</f>
         <v>197.90859999999995</v>
       </c>
       <c r="U88" s="5">
+        <f t="shared" si="20"/>
+        <v>197.90859999999995</v>
+      </c>
+      <c r="V88" s="1"/>
+      <c r="W88" s="1">
+        <f t="shared" si="21"/>
+        <v>10.5</v>
+      </c>
+      <c r="X88" s="1">
         <f t="shared" si="19"/>
-        <v>197.90859999999995</v>
-      </c>
-      <c r="V88" s="19"/>
-      <c r="W88" s="1">
-        <f t="shared" si="20"/>
-        <v>10.5</v>
-      </c>
-      <c r="X88" s="1">
-        <f t="shared" si="18"/>
         <v>5.6352293397571414</v>
       </c>
       <c r="Y88" s="1">
@@ -10243,10 +10482,13 @@
       </c>
       <c r="AI88" s="1"/>
       <c r="AJ88" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>198</v>
       </c>
-      <c r="AK88" s="1"/>
+      <c r="AK88" s="1">
+        <f t="shared" si="23"/>
+        <v>39.707363636363631</v>
+      </c>
       <c r="AL88" s="1"/>
       <c r="AM88" s="1"/>
       <c r="AN88" s="1"/>
@@ -10287,7 +10529,7 @@
         <v>824.90499999999997</v>
       </c>
       <c r="L89" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-3.1609999999999445</v>
       </c>
       <c r="M89" s="1"/>
@@ -10299,21 +10541,21 @@
       </c>
       <c r="R89" s="1"/>
       <c r="S89" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>164.34880000000001</v>
       </c>
       <c r="T89" s="5"/>
       <c r="U89" s="5">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="V89" s="1"/>
+      <c r="W89" s="1">
+        <f t="shared" si="21"/>
+        <v>12.835885111421561</v>
+      </c>
+      <c r="X89" s="1">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V89" s="19"/>
-      <c r="W89" s="1">
-        <f t="shared" si="20"/>
-        <v>12.835885111421561</v>
-      </c>
-      <c r="X89" s="1">
-        <f t="shared" si="18"/>
         <v>12.835885111421561</v>
       </c>
       <c r="Y89" s="1">
@@ -10348,10 +10590,13 @@
       </c>
       <c r="AI89" s="1"/>
       <c r="AJ89" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AK89" s="1"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AK89" s="1">
+        <f t="shared" si="23"/>
+        <v>177.93881818181816</v>
+      </c>
       <c r="AL89" s="1"/>
       <c r="AM89" s="1"/>
       <c r="AN89" s="1"/>
@@ -10380,7 +10625,7 @@
       <c r="J90" s="11"/>
       <c r="K90" s="11"/>
       <c r="L90" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M90" s="11"/>
@@ -10392,21 +10637,21 @@
       </c>
       <c r="R90" s="11"/>
       <c r="S90" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="T90" s="13"/>
       <c r="U90" s="5">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="V90" s="11"/>
+      <c r="W90" s="1" t="e">
+        <f t="shared" si="21"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X90" s="11" t="e">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V90" s="20"/>
-      <c r="W90" s="1" t="e">
-        <f t="shared" si="20"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X90" s="11" t="e">
-        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y90" s="11">
@@ -10443,10 +10688,13 @@
         <v>43</v>
       </c>
       <c r="AJ90" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AK90" s="1"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AK90" s="1">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="AL90" s="1"/>
       <c r="AM90" s="1"/>
       <c r="AN90" s="1"/>
@@ -10487,7 +10735,7 @@
         <v>1998.35</v>
       </c>
       <c r="L91" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-42.453999999999951</v>
       </c>
       <c r="M91" s="1"/>
@@ -10501,20 +10749,20 @@
       </c>
       <c r="R91" s="1"/>
       <c r="S91" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>391.17919999999998</v>
       </c>
       <c r="T91" s="5"/>
-      <c r="U91" s="27">
+      <c r="U91" s="20">
         <v>500</v>
       </c>
-      <c r="V91" s="19"/>
+      <c r="V91" s="1"/>
       <c r="W91" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>13.545035114341459</v>
       </c>
       <c r="X91" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>12.266848544094369</v>
       </c>
       <c r="Y91" s="1">
@@ -10549,10 +10797,13 @@
       </c>
       <c r="AI91" s="1"/>
       <c r="AJ91" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>500</v>
       </c>
-      <c r="AK91" s="1"/>
+      <c r="AK91" s="1">
+        <f t="shared" si="23"/>
+        <v>419.75401818181814</v>
+      </c>
       <c r="AL91" s="1"/>
       <c r="AM91" s="1"/>
       <c r="AN91" s="1"/>
@@ -10593,7 +10844,7 @@
         <v>2032.9</v>
       </c>
       <c r="L92" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-26.294000000000096</v>
       </c>
       <c r="M92" s="1"/>
@@ -10609,21 +10860,21 @@
         <v>800</v>
       </c>
       <c r="S92" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>401.32119999999998</v>
       </c>
       <c r="T92" s="5"/>
       <c r="U92" s="5">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="V92" s="1"/>
+      <c r="W92" s="1">
+        <f t="shared" si="21"/>
+        <v>19.361381855730524</v>
+      </c>
+      <c r="X92" s="1">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V92" s="19"/>
-      <c r="W92" s="1">
-        <f t="shared" si="20"/>
-        <v>19.361381855730524</v>
-      </c>
-      <c r="X92" s="1">
-        <f t="shared" si="18"/>
         <v>19.361381855730524</v>
       </c>
       <c r="Y92" s="1">
@@ -10658,10 +10909,13 @@
       </c>
       <c r="AI92" s="1"/>
       <c r="AJ92" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AK92" s="1"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AK92" s="1">
+        <f t="shared" si="23"/>
+        <v>500.76589090909096</v>
+      </c>
       <c r="AL92" s="1"/>
       <c r="AM92" s="1"/>
       <c r="AN92" s="1"/>
@@ -10702,7 +10956,7 @@
         <v>2966.75</v>
       </c>
       <c r="L93" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-40.6550000000002</v>
       </c>
       <c r="M93" s="1"/>
@@ -10720,21 +10974,21 @@
         <v>1200</v>
       </c>
       <c r="S93" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>585.21899999999994</v>
       </c>
       <c r="T93" s="5"/>
       <c r="U93" s="5">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="V93" s="1"/>
+      <c r="W93" s="1">
+        <f t="shared" si="21"/>
+        <v>18.625799914220149</v>
+      </c>
+      <c r="X93" s="1">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V93" s="19"/>
-      <c r="W93" s="1">
-        <f t="shared" si="20"/>
-        <v>18.625799914220149</v>
-      </c>
-      <c r="X93" s="1">
-        <f t="shared" si="18"/>
         <v>18.625799914220149</v>
       </c>
       <c r="Y93" s="1">
@@ -10769,10 +11023,13 @@
       </c>
       <c r="AI93" s="1"/>
       <c r="AJ93" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AK93" s="1"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AK93" s="1">
+        <f t="shared" si="23"/>
+        <v>593.22269090909094</v>
+      </c>
       <c r="AL93" s="1"/>
       <c r="AM93" s="1"/>
       <c r="AN93" s="1"/>
@@ -10811,7 +11068,7 @@
         <v>39</v>
       </c>
       <c r="L94" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>5.597999999999999</v>
       </c>
       <c r="M94" s="1"/>
@@ -10823,23 +11080,23 @@
       </c>
       <c r="R94" s="1"/>
       <c r="S94" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>8.9195999999999991</v>
       </c>
       <c r="T94" s="5">
         <v>10</v>
       </c>
       <c r="U94" s="5">
+        <f t="shared" si="20"/>
+        <v>10</v>
+      </c>
+      <c r="V94" s="1"/>
+      <c r="W94" s="1">
+        <f t="shared" si="21"/>
+        <v>11.568769899995516</v>
+      </c>
+      <c r="X94" s="1">
         <f t="shared" si="19"/>
-        <v>10</v>
-      </c>
-      <c r="V94" s="19"/>
-      <c r="W94" s="1">
-        <f t="shared" si="20"/>
-        <v>11.568769899995516</v>
-      </c>
-      <c r="X94" s="1">
-        <f t="shared" si="18"/>
         <v>10.447643392080364</v>
       </c>
       <c r="Y94" s="1">
@@ -10874,10 +11131,13 @@
       </c>
       <c r="AI94" s="1"/>
       <c r="AJ94" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>10</v>
       </c>
-      <c r="AK94" s="1"/>
+      <c r="AK94" s="1">
+        <f t="shared" si="23"/>
+        <v>8.3002000000000002</v>
+      </c>
       <c r="AL94" s="1"/>
       <c r="AM94" s="1"/>
       <c r="AN94" s="1"/>
@@ -10916,7 +11176,7 @@
         <v>18.3</v>
       </c>
       <c r="L95" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.62599999999999767</v>
       </c>
       <c r="M95" s="11"/>
@@ -10928,21 +11188,21 @@
       </c>
       <c r="R95" s="11"/>
       <c r="S95" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>3.7851999999999997</v>
       </c>
       <c r="T95" s="13"/>
       <c r="U95" s="5">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="V95" s="11"/>
+      <c r="W95" s="1">
+        <f t="shared" si="21"/>
+        <v>7.1346296100602355</v>
+      </c>
+      <c r="X95" s="11">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V95" s="20"/>
-      <c r="W95" s="1">
-        <f t="shared" si="20"/>
-        <v>7.1346296100602355</v>
-      </c>
-      <c r="X95" s="11">
-        <f t="shared" si="18"/>
         <v>7.1346296100602355</v>
       </c>
       <c r="Y95" s="11">
@@ -10979,10 +11239,13 @@
         <v>83</v>
       </c>
       <c r="AJ95" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AK95" s="1"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AK95" s="1">
+        <f t="shared" si="23"/>
+        <v>3.6625272727272731</v>
+      </c>
       <c r="AL95" s="1"/>
       <c r="AM95" s="1"/>
       <c r="AN95" s="1"/>
@@ -11017,7 +11280,7 @@
         <v>10.4</v>
       </c>
       <c r="L96" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>6.0999999999999943E-2</v>
       </c>
       <c r="M96" s="11"/>
@@ -11029,21 +11292,21 @@
       </c>
       <c r="R96" s="11"/>
       <c r="S96" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2.0922000000000001</v>
       </c>
       <c r="T96" s="13"/>
       <c r="U96" s="5">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="V96" s="11"/>
+      <c r="W96" s="1">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="X96" s="11">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V96" s="20"/>
-      <c r="W96" s="1">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="X96" s="11">
-        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Y96" s="11">
@@ -11080,10 +11343,13 @@
         <v>136</v>
       </c>
       <c r="AJ96" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AK96" s="1"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AK96" s="1">
+        <f t="shared" si="23"/>
+        <v>1.3224181818181817</v>
+      </c>
       <c r="AL96" s="1"/>
       <c r="AM96" s="1"/>
       <c r="AN96" s="1"/>
@@ -11124,7 +11390,7 @@
         <v>50</v>
       </c>
       <c r="L97" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-26</v>
       </c>
       <c r="M97" s="1"/>
@@ -11136,21 +11402,21 @@
       </c>
       <c r="R97" s="1"/>
       <c r="S97" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>4.8</v>
       </c>
       <c r="T97" s="5"/>
       <c r="U97" s="5">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="V97" s="1"/>
+      <c r="W97" s="1">
+        <f t="shared" si="21"/>
+        <v>116.875</v>
+      </c>
+      <c r="X97" s="1">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V97" s="19"/>
-      <c r="W97" s="1">
-        <f t="shared" si="20"/>
-        <v>116.875</v>
-      </c>
-      <c r="X97" s="1">
-        <f t="shared" si="18"/>
         <v>116.875</v>
       </c>
       <c r="Y97" s="1">
@@ -11185,10 +11451,13 @@
       </c>
       <c r="AI97" s="1"/>
       <c r="AJ97" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AK97" s="1"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AK97" s="1">
+        <f t="shared" si="23"/>
+        <v>42.345454545454551</v>
+      </c>
       <c r="AL97" s="1"/>
       <c r="AM97" s="1"/>
       <c r="AN97" s="1"/>
@@ -11229,7 +11498,7 @@
         <v>390</v>
       </c>
       <c r="L98" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-4</v>
       </c>
       <c r="M98" s="1"/>
@@ -11241,7 +11510,7 @@
       </c>
       <c r="R98" s="1"/>
       <c r="S98" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>77.2</v>
       </c>
       <c r="T98" s="5">
@@ -11249,16 +11518,16 @@
         <v>429.40000000000003</v>
       </c>
       <c r="U98" s="5">
+        <f t="shared" si="20"/>
+        <v>429.40000000000003</v>
+      </c>
+      <c r="V98" s="1"/>
+      <c r="W98" s="1">
+        <f t="shared" si="21"/>
+        <v>8</v>
+      </c>
+      <c r="X98" s="1">
         <f t="shared" si="19"/>
-        <v>429.40000000000003</v>
-      </c>
-      <c r="V98" s="19"/>
-      <c r="W98" s="1">
-        <f t="shared" si="20"/>
-        <v>8</v>
-      </c>
-      <c r="X98" s="1">
-        <f t="shared" si="18"/>
         <v>2.437823834196891</v>
       </c>
       <c r="Y98" s="1">
@@ -11293,10 +11562,13 @@
       </c>
       <c r="AI98" s="1"/>
       <c r="AJ98" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>129</v>
       </c>
-      <c r="AK98" s="1"/>
+      <c r="AK98" s="1">
+        <f t="shared" si="23"/>
+        <v>36.545454545454554</v>
+      </c>
       <c r="AL98" s="1"/>
       <c r="AM98" s="1"/>
       <c r="AN98" s="1"/>
@@ -11327,7 +11599,7 @@
         <v>11</v>
       </c>
       <c r="L99" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-11</v>
       </c>
       <c r="M99" s="11"/>
@@ -11339,21 +11611,21 @@
       </c>
       <c r="R99" s="11"/>
       <c r="S99" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="T99" s="13"/>
       <c r="U99" s="5">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="V99" s="11"/>
+      <c r="W99" s="1" t="e">
+        <f t="shared" si="21"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X99" s="11" t="e">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V99" s="20"/>
-      <c r="W99" s="1" t="e">
-        <f t="shared" si="20"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X99" s="11" t="e">
-        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y99" s="11">
@@ -11390,10 +11662,13 @@
         <v>43</v>
       </c>
       <c r="AJ99" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AK99" s="1"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AK99" s="1">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="AL99" s="1"/>
       <c r="AM99" s="1"/>
       <c r="AN99" s="1"/>
@@ -11432,7 +11707,7 @@
         <v>225</v>
       </c>
       <c r="L100" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-5</v>
       </c>
       <c r="M100" s="1"/>
@@ -11444,24 +11719,24 @@
       </c>
       <c r="R100" s="1"/>
       <c r="S100" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>44</v>
       </c>
       <c r="T100" s="5">
-        <f t="shared" ref="T100:T101" si="23">10.5*S100-R100-Q100-P100-O100-F100</f>
+        <f t="shared" ref="T100:T101" si="25">10.5*S100-R100-Q100-P100-O100-F100</f>
         <v>195</v>
       </c>
       <c r="U100" s="5">
+        <f t="shared" si="20"/>
+        <v>195</v>
+      </c>
+      <c r="V100" s="1"/>
+      <c r="W100" s="1">
+        <f t="shared" si="21"/>
+        <v>10.5</v>
+      </c>
+      <c r="X100" s="1">
         <f t="shared" si="19"/>
-        <v>195</v>
-      </c>
-      <c r="V100" s="19"/>
-      <c r="W100" s="1">
-        <f t="shared" si="20"/>
-        <v>10.5</v>
-      </c>
-      <c r="X100" s="1">
-        <f t="shared" si="18"/>
         <v>6.0681818181818183</v>
       </c>
       <c r="Y100" s="1">
@@ -11496,10 +11771,13 @@
       </c>
       <c r="AI100" s="1"/>
       <c r="AJ100" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>14</v>
       </c>
-      <c r="AK100" s="1"/>
+      <c r="AK100" s="1">
+        <f t="shared" si="23"/>
+        <v>33.909090909090907</v>
+      </c>
       <c r="AL100" s="1"/>
       <c r="AM100" s="1"/>
       <c r="AN100" s="1"/>
@@ -11540,7 +11818,7 @@
         <v>173</v>
       </c>
       <c r="L101" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-6</v>
       </c>
       <c r="M101" s="1"/>
@@ -11552,24 +11830,24 @@
       </c>
       <c r="R101" s="1"/>
       <c r="S101" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>33.4</v>
       </c>
       <c r="T101" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>139.88799999999998</v>
       </c>
       <c r="U101" s="5">
+        <f t="shared" si="20"/>
+        <v>139.88799999999998</v>
+      </c>
+      <c r="V101" s="1"/>
+      <c r="W101" s="1">
+        <f t="shared" si="21"/>
+        <v>10.5</v>
+      </c>
+      <c r="X101" s="1">
         <f t="shared" si="19"/>
-        <v>139.88799999999998</v>
-      </c>
-      <c r="V101" s="19"/>
-      <c r="W101" s="1">
-        <f t="shared" si="20"/>
-        <v>10.5</v>
-      </c>
-      <c r="X101" s="1">
-        <f t="shared" si="18"/>
         <v>6.3117365269461088</v>
       </c>
       <c r="Y101" s="1">
@@ -11604,10 +11882,13 @@
       </c>
       <c r="AI101" s="1"/>
       <c r="AJ101" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>10</v>
       </c>
-      <c r="AK101" s="1"/>
+      <c r="AK101" s="1">
+        <f t="shared" si="23"/>
+        <v>26.363636363636363</v>
+      </c>
       <c r="AL101" s="1"/>
       <c r="AM101" s="1"/>
       <c r="AN101" s="1"/>
@@ -11646,7 +11927,7 @@
         <v>132</v>
       </c>
       <c r="L102" s="11">
-        <f t="shared" ref="L102:L133" si="24">E102-K102</f>
+        <f t="shared" ref="L102:L133" si="26">E102-K102</f>
         <v>-7</v>
       </c>
       <c r="M102" s="11"/>
@@ -11658,21 +11939,21 @@
       </c>
       <c r="R102" s="11"/>
       <c r="S102" s="11">
-        <f t="shared" ref="S102:S135" si="25">E102/5</f>
+        <f t="shared" ref="S102:S135" si="27">E102/5</f>
         <v>25</v>
       </c>
       <c r="T102" s="13"/>
       <c r="U102" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V102" s="20"/>
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="V102" s="11"/>
       <c r="W102" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.32</v>
       </c>
       <c r="X102" s="11">
-        <f t="shared" ref="X102:X135" si="26">(F102+O102+P102+Q102+R102)/S102</f>
+        <f t="shared" ref="X102:X135" si="28">(F102+O102+P102+Q102+R102)/S102</f>
         <v>0.32</v>
       </c>
       <c r="Y102" s="11">
@@ -11707,10 +11988,13 @@
       </c>
       <c r="AI102" s="11"/>
       <c r="AJ102" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AK102" s="1"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AK102" s="1">
+        <f t="shared" si="23"/>
+        <v>18.618181818181817</v>
+      </c>
       <c r="AL102" s="1"/>
       <c r="AM102" s="1"/>
       <c r="AN102" s="1"/>
@@ -11749,7 +12033,7 @@
         <v>202</v>
       </c>
       <c r="L103" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>-202</v>
       </c>
       <c r="M103" s="1"/>
@@ -11761,21 +12045,21 @@
       </c>
       <c r="R103" s="1"/>
       <c r="S103" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="T103" s="5"/>
       <c r="U103" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V103" s="19"/>
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="V103" s="1"/>
       <c r="W103" s="1" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X103" s="1" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y103" s="1">
@@ -11810,10 +12094,13 @@
       </c>
       <c r="AI103" s="1"/>
       <c r="AJ103" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AK103" s="1"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AK103" s="1">
+        <f t="shared" si="23"/>
+        <v>32.599999999999994</v>
+      </c>
       <c r="AL103" s="1"/>
       <c r="AM103" s="1"/>
       <c r="AN103" s="1"/>
@@ -11854,7 +12141,7 @@
         <v>65.7</v>
       </c>
       <c r="L104" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>7.4140000000000015</v>
       </c>
       <c r="M104" s="1"/>
@@ -11866,21 +12153,21 @@
       </c>
       <c r="R104" s="1"/>
       <c r="S104" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>14.622800000000002</v>
       </c>
       <c r="T104" s="5"/>
       <c r="U104" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V104" s="19"/>
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="V104" s="1"/>
       <c r="W104" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>13.665235112290395</v>
       </c>
       <c r="X104" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>13.665235112290395</v>
       </c>
       <c r="Y104" s="1">
@@ -11915,10 +12202,13 @@
       </c>
       <c r="AI104" s="1"/>
       <c r="AJ104" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AK104" s="1"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AK104" s="1">
+        <f t="shared" si="23"/>
+        <v>18.637599999999999</v>
+      </c>
       <c r="AL104" s="1"/>
       <c r="AM104" s="1"/>
       <c r="AN104" s="1"/>
@@ -11949,7 +12239,7 @@
         <v>6</v>
       </c>
       <c r="L105" s="11">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>-6</v>
       </c>
       <c r="M105" s="11"/>
@@ -11961,21 +12251,21 @@
       </c>
       <c r="R105" s="11"/>
       <c r="S105" s="11">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="T105" s="13"/>
       <c r="U105" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V105" s="20"/>
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="V105" s="11"/>
       <c r="W105" s="1" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X105" s="11" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y105" s="11">
@@ -12012,10 +12302,13 @@
         <v>43</v>
       </c>
       <c r="AJ105" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AK105" s="1"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AK105" s="1">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="AL105" s="1"/>
       <c r="AM105" s="1"/>
       <c r="AN105" s="1"/>
@@ -12054,7 +12347,7 @@
         <v>23</v>
       </c>
       <c r="L106" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>-9</v>
       </c>
       <c r="M106" s="1"/>
@@ -12066,7 +12359,7 @@
       </c>
       <c r="R106" s="1"/>
       <c r="S106" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>2.8</v>
       </c>
       <c r="T106" s="5">
@@ -12074,16 +12367,16 @@
         <v>16.799999999999997</v>
       </c>
       <c r="U106" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>16.799999999999997</v>
       </c>
-      <c r="V106" s="19"/>
+      <c r="V106" s="1"/>
       <c r="W106" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5.9999999999999991</v>
       </c>
       <c r="X106" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="Y106" s="1">
@@ -12118,10 +12411,13 @@
       </c>
       <c r="AI106" s="1"/>
       <c r="AJ106" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>2</v>
       </c>
-      <c r="AK106" s="1"/>
+      <c r="AK106" s="1">
+        <f t="shared" si="23"/>
+        <v>1.781818181818182</v>
+      </c>
       <c r="AL106" s="1"/>
       <c r="AM106" s="1"/>
       <c r="AN106" s="1"/>
@@ -12162,7 +12458,7 @@
         <v>225</v>
       </c>
       <c r="L107" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>-9</v>
       </c>
       <c r="M107" s="1"/>
@@ -12174,24 +12470,24 @@
       </c>
       <c r="R107" s="1"/>
       <c r="S107" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>43.2</v>
       </c>
       <c r="T107" s="5">
-        <f t="shared" ref="T107:T112" si="27">10.5*S107-R107-Q107-P107-O107-F107</f>
+        <f t="shared" ref="T107:T112" si="29">10.5*S107-R107-Q107-P107-O107-F107</f>
         <v>96.93200000000013</v>
       </c>
       <c r="U107" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>96.93200000000013</v>
       </c>
-      <c r="V107" s="19"/>
+      <c r="V107" s="1"/>
       <c r="W107" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>10.5</v>
       </c>
       <c r="X107" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>8.2562037037037008</v>
       </c>
       <c r="Y107" s="1">
@@ -12226,10 +12522,13 @@
       </c>
       <c r="AI107" s="1"/>
       <c r="AJ107" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>8</v>
       </c>
-      <c r="AK107" s="1"/>
+      <c r="AK107" s="1">
+        <f t="shared" si="23"/>
+        <v>43.945454545454545</v>
+      </c>
       <c r="AL107" s="1"/>
       <c r="AM107" s="1"/>
       <c r="AN107" s="1"/>
@@ -12270,7 +12569,7 @@
         <v>246</v>
       </c>
       <c r="L108" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>-3</v>
       </c>
       <c r="M108" s="1"/>
@@ -12282,24 +12581,24 @@
       </c>
       <c r="R108" s="1"/>
       <c r="S108" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>48.6</v>
       </c>
       <c r="T108" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>278.3</v>
       </c>
       <c r="U108" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>278.3</v>
       </c>
-      <c r="V108" s="19"/>
+      <c r="V108" s="1"/>
       <c r="W108" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>10.5</v>
       </c>
       <c r="X108" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>4.7736625514403288</v>
       </c>
       <c r="Y108" s="1">
@@ -12334,10 +12633,13 @@
       </c>
       <c r="AI108" s="1"/>
       <c r="AJ108" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>22</v>
       </c>
-      <c r="AK108" s="1"/>
+      <c r="AK108" s="1">
+        <f t="shared" si="23"/>
+        <v>33.927272727272729</v>
+      </c>
       <c r="AL108" s="1"/>
       <c r="AM108" s="1"/>
       <c r="AN108" s="1"/>
@@ -12376,7 +12678,7 @@
         <v>23</v>
       </c>
       <c r="L109" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>-2</v>
       </c>
       <c r="M109" s="1"/>
@@ -12388,7 +12690,7 @@
       </c>
       <c r="R109" s="1"/>
       <c r="S109" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>4.2</v>
       </c>
       <c r="T109" s="5">
@@ -12396,16 +12698,16 @@
         <v>26.200000000000003</v>
       </c>
       <c r="U109" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>26.200000000000003</v>
       </c>
-      <c r="V109" s="19"/>
+      <c r="V109" s="1"/>
       <c r="W109" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>6</v>
       </c>
       <c r="X109" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-0.23809523809523808</v>
       </c>
       <c r="Y109" s="1">
@@ -12442,10 +12744,13 @@
         <v>150</v>
       </c>
       <c r="AJ109" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>4</v>
       </c>
-      <c r="AK109" s="1"/>
+      <c r="AK109" s="1">
+        <f t="shared" si="23"/>
+        <v>1.5090909090909088</v>
+      </c>
       <c r="AL109" s="1"/>
       <c r="AM109" s="1"/>
       <c r="AN109" s="1"/>
@@ -12486,7 +12791,7 @@
         <v>412.65</v>
       </c>
       <c r="L110" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>-9.7829999999999586</v>
       </c>
       <c r="M110" s="1"/>
@@ -12498,21 +12803,21 @@
       </c>
       <c r="R110" s="1"/>
       <c r="S110" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>80.573400000000007</v>
       </c>
       <c r="T110" s="5"/>
       <c r="U110" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V110" s="19"/>
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="V110" s="1"/>
       <c r="W110" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>11.942846745948408</v>
       </c>
       <c r="X110" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>11.942846745948408</v>
       </c>
       <c r="Y110" s="1">
@@ -12547,10 +12852,13 @@
       </c>
       <c r="AI110" s="1"/>
       <c r="AJ110" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AK110" s="1"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AK110" s="1">
+        <f t="shared" si="23"/>
+        <v>75.951145454545454</v>
+      </c>
       <c r="AL110" s="1"/>
       <c r="AM110" s="1"/>
       <c r="AN110" s="1"/>
@@ -12591,7 +12899,7 @@
         <v>296.89999999999998</v>
       </c>
       <c r="L111" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>-2.7439999999999714</v>
       </c>
       <c r="M111" s="1"/>
@@ -12603,21 +12911,21 @@
       </c>
       <c r="R111" s="1"/>
       <c r="S111" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>58.831200000000003</v>
       </c>
       <c r="T111" s="5"/>
       <c r="U111" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V111" s="19"/>
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="V111" s="1"/>
       <c r="W111" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>13.159072634928407</v>
       </c>
       <c r="X111" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>13.159072634928407</v>
       </c>
       <c r="Y111" s="1">
@@ -12652,10 +12960,13 @@
       </c>
       <c r="AI111" s="1"/>
       <c r="AJ111" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AK111" s="1"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AK111" s="1">
+        <f t="shared" si="23"/>
+        <v>51.1620909090909</v>
+      </c>
       <c r="AL111" s="1"/>
       <c r="AM111" s="1"/>
       <c r="AN111" s="1"/>
@@ -12697,7 +13008,7 @@
         <v>464.6</v>
       </c>
       <c r="L112" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>-17.076999999999998</v>
       </c>
       <c r="M112" s="1"/>
@@ -12709,24 +13020,24 @@
       </c>
       <c r="R112" s="1"/>
       <c r="S112" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>89.504600000000011</v>
       </c>
       <c r="T112" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>70.279300000000148</v>
       </c>
       <c r="U112" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>70.279300000000148</v>
       </c>
-      <c r="V112" s="19"/>
+      <c r="V112" s="1"/>
       <c r="W112" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>10.5</v>
       </c>
       <c r="X112" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>9.7147967813944742</v>
       </c>
       <c r="Y112" s="1">
@@ -12761,10 +13072,13 @@
       </c>
       <c r="AI112" s="1"/>
       <c r="AJ112" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>70</v>
       </c>
-      <c r="AK112" s="1"/>
+      <c r="AK112" s="1">
+        <f t="shared" si="23"/>
+        <v>89.746872727272731</v>
+      </c>
       <c r="AL112" s="1"/>
       <c r="AM112" s="1"/>
       <c r="AN112" s="1"/>
@@ -12793,7 +13107,7 @@
       <c r="J113" s="11"/>
       <c r="K113" s="11"/>
       <c r="L113" s="11">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="M113" s="11"/>
@@ -12805,21 +13119,21 @@
       </c>
       <c r="R113" s="11"/>
       <c r="S113" s="11">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="T113" s="13"/>
       <c r="U113" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V113" s="20"/>
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="V113" s="11"/>
       <c r="W113" s="1" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X113" s="11" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y113" s="11">
@@ -12856,10 +13170,13 @@
         <v>43</v>
       </c>
       <c r="AJ113" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AK113" s="1"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AK113" s="1">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="AL113" s="1"/>
       <c r="AM113" s="1"/>
       <c r="AN113" s="1"/>
@@ -12898,7 +13215,7 @@
         <v>5.9</v>
       </c>
       <c r="L114" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0.80399999999999938</v>
       </c>
       <c r="M114" s="1"/>
@@ -12910,21 +13227,21 @@
       </c>
       <c r="R114" s="1"/>
       <c r="S114" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1.3408</v>
       </c>
       <c r="T114" s="5"/>
       <c r="U114" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V114" s="19"/>
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="V114" s="1"/>
       <c r="W114" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>13.884248210023866</v>
       </c>
       <c r="X114" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>13.884248210023866</v>
       </c>
       <c r="Y114" s="1">
@@ -12961,10 +13278,13 @@
         <v>181</v>
       </c>
       <c r="AJ114" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AK114" s="1"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AK114" s="1">
+        <f t="shared" si="23"/>
+        <v>1.1533454545454545</v>
+      </c>
       <c r="AL114" s="1"/>
       <c r="AM114" s="1"/>
       <c r="AN114" s="1"/>
@@ -13005,7 +13325,7 @@
         <v>447</v>
       </c>
       <c r="L115" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>-15</v>
       </c>
       <c r="M115" s="1"/>
@@ -13017,24 +13337,24 @@
       </c>
       <c r="R115" s="1"/>
       <c r="S115" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>86.4</v>
       </c>
       <c r="T115" s="5">
-        <f t="shared" ref="T115" si="28">10.5*S115-R115-Q115-P115-O115-F115</f>
+        <f t="shared" ref="T115" si="30">10.5*S115-R115-Q115-P115-O115-F115</f>
         <v>272.83900000000006</v>
       </c>
       <c r="U115" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>272.83900000000006</v>
       </c>
-      <c r="V115" s="19"/>
+      <c r="V115" s="1"/>
       <c r="W115" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>10.5</v>
       </c>
       <c r="X115" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>7.3421412037037035</v>
       </c>
       <c r="Y115" s="1">
@@ -13069,10 +13389,13 @@
       </c>
       <c r="AI115" s="1"/>
       <c r="AJ115" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>76</v>
       </c>
-      <c r="AK115" s="1"/>
+      <c r="AK115" s="1">
+        <f t="shared" si="23"/>
+        <v>65.672727272727258</v>
+      </c>
       <c r="AL115" s="1"/>
       <c r="AM115" s="1"/>
       <c r="AN115" s="1"/>
@@ -13101,7 +13424,7 @@
       <c r="J116" s="11"/>
       <c r="K116" s="11"/>
       <c r="L116" s="11">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="M116" s="11"/>
@@ -13113,21 +13436,21 @@
       </c>
       <c r="R116" s="11"/>
       <c r="S116" s="11">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="T116" s="13"/>
       <c r="U116" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V116" s="20"/>
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="V116" s="11"/>
       <c r="W116" s="1" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X116" s="11" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y116" s="11">
@@ -13164,10 +13487,13 @@
         <v>43</v>
       </c>
       <c r="AJ116" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AK116" s="1"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AK116" s="1">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="AL116" s="1"/>
       <c r="AM116" s="1"/>
       <c r="AN116" s="1"/>
@@ -13208,7 +13534,7 @@
         <v>369</v>
       </c>
       <c r="L117" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>-24</v>
       </c>
       <c r="M117" s="1"/>
@@ -13220,21 +13546,21 @@
       </c>
       <c r="R117" s="1"/>
       <c r="S117" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>69</v>
       </c>
       <c r="T117" s="5"/>
       <c r="U117" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V117" s="19"/>
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="V117" s="1"/>
       <c r="W117" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>10.711521739130434</v>
       </c>
       <c r="X117" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>10.711521739130434</v>
       </c>
       <c r="Y117" s="1">
@@ -13269,10 +13595,13 @@
       </c>
       <c r="AI117" s="1"/>
       <c r="AJ117" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AK117" s="1"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AK117" s="1">
+        <f t="shared" si="23"/>
+        <v>64.090909090909108</v>
+      </c>
       <c r="AL117" s="1"/>
       <c r="AM117" s="1"/>
       <c r="AN117" s="1"/>
@@ -13280,102 +13609,105 @@
       <c r="AP117" s="1"/>
       <c r="AQ117" s="1"/>
     </row>
-    <row r="118" spans="1:43" s="26" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="22" t="s">
+    <row r="118" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A118" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B118" s="22" t="s">
+      <c r="B118" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C118" s="22"/>
-      <c r="D118" s="22"/>
-      <c r="E118" s="22"/>
-      <c r="F118" s="22"/>
-      <c r="G118" s="23">
+      <c r="C118" s="1"/>
+      <c r="D118" s="1"/>
+      <c r="E118" s="1"/>
+      <c r="F118" s="1"/>
+      <c r="G118" s="7">
         <v>0.09</v>
       </c>
-      <c r="H118" s="22"/>
-      <c r="I118" s="22" t="s">
+      <c r="H118" s="1"/>
+      <c r="I118" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="J118" s="22"/>
-      <c r="K118" s="22"/>
-      <c r="L118" s="22">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="M118" s="22"/>
-      <c r="N118" s="22"/>
-      <c r="O118" s="22"/>
-      <c r="P118" s="22"/>
-      <c r="Q118" s="22">
-        <v>0</v>
-      </c>
-      <c r="R118" s="22"/>
-      <c r="S118" s="22">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="T118" s="24"/>
+      <c r="J118" s="1"/>
+      <c r="K118" s="1"/>
+      <c r="L118" s="1">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="M118" s="1"/>
+      <c r="N118" s="1"/>
+      <c r="O118" s="1"/>
+      <c r="P118" s="1"/>
+      <c r="Q118" s="1">
+        <v>0</v>
+      </c>
+      <c r="R118" s="1"/>
+      <c r="S118" s="1">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="T118" s="5"/>
       <c r="U118" s="5">
         <f>V118</f>
         <v>30</v>
       </c>
-      <c r="V118" s="25">
+      <c r="V118" s="1">
         <v>30</v>
       </c>
       <c r="W118" s="1" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X118" s="22" t="e">
-        <f t="shared" si="26"/>
+      <c r="X118" s="1" t="e">
+        <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y118" s="22">
-        <v>0</v>
-      </c>
-      <c r="Z118" s="22">
-        <v>0</v>
-      </c>
-      <c r="AA118" s="22">
-        <v>0</v>
-      </c>
-      <c r="AB118" s="22">
-        <v>0</v>
-      </c>
-      <c r="AC118" s="22">
-        <v>0</v>
-      </c>
-      <c r="AD118" s="22">
-        <v>0</v>
-      </c>
-      <c r="AE118" s="22">
-        <v>0</v>
-      </c>
-      <c r="AF118" s="22">
-        <v>0</v>
-      </c>
-      <c r="AG118" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH118" s="22">
-        <v>0</v>
-      </c>
-      <c r="AI118" s="22" t="s">
+      <c r="Y118" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z118" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA118" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB118" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC118" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD118" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE118" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF118" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG118" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH118" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI118" s="1" t="s">
         <v>184</v>
       </c>
       <c r="AJ118" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>3</v>
       </c>
-      <c r="AK118" s="22"/>
-      <c r="AL118" s="22"/>
-      <c r="AM118" s="22"/>
-      <c r="AN118" s="22"/>
-      <c r="AO118" s="22"/>
-      <c r="AP118" s="22"/>
-      <c r="AQ118" s="22"/>
+      <c r="AK118" s="1">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AL118" s="1"/>
+      <c r="AM118" s="1"/>
+      <c r="AN118" s="1"/>
+      <c r="AO118" s="1"/>
+      <c r="AP118" s="1"/>
+      <c r="AQ118" s="1"/>
     </row>
     <row r="119" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
@@ -13410,7 +13742,7 @@
         <v>135</v>
       </c>
       <c r="L119" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>-49.152000000000001</v>
       </c>
       <c r="M119" s="1"/>
@@ -13422,21 +13754,21 @@
       </c>
       <c r="R119" s="1"/>
       <c r="S119" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>17.169599999999999</v>
       </c>
       <c r="T119" s="5"/>
       <c r="U119" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V119" s="19"/>
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="V119" s="1"/>
       <c r="W119" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>15.169543844935234</v>
       </c>
       <c r="X119" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>15.169543844935234</v>
       </c>
       <c r="Y119" s="1">
@@ -13471,10 +13803,13 @@
       </c>
       <c r="AI119" s="1"/>
       <c r="AJ119" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AK119" s="1"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AK119" s="1">
+        <f t="shared" si="23"/>
+        <v>32.2316</v>
+      </c>
       <c r="AL119" s="1"/>
       <c r="AM119" s="1"/>
       <c r="AN119" s="1"/>
@@ -13515,7 +13850,7 @@
         <v>72.5</v>
       </c>
       <c r="L120" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>-70.691999999999993</v>
       </c>
       <c r="M120" s="1"/>
@@ -13527,21 +13862,21 @@
       </c>
       <c r="R120" s="1"/>
       <c r="S120" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0.36160000000000003</v>
       </c>
       <c r="T120" s="5"/>
       <c r="U120" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V120" s="19"/>
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="V120" s="1"/>
       <c r="W120" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>227.01880530973449</v>
       </c>
       <c r="X120" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>227.01880530973449</v>
       </c>
       <c r="Y120" s="1">
@@ -13578,10 +13913,13 @@
         <v>180</v>
       </c>
       <c r="AJ120" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AK120" s="1"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AK120" s="1">
+        <f t="shared" si="23"/>
+        <v>12.761709090909092</v>
+      </c>
       <c r="AL120" s="1"/>
       <c r="AM120" s="1"/>
       <c r="AN120" s="1"/>
@@ -13589,102 +13927,105 @@
       <c r="AP120" s="1"/>
       <c r="AQ120" s="1"/>
     </row>
-    <row r="121" spans="1:43" s="26" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="22" t="s">
+    <row r="121" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A121" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="B121" s="22" t="s">
+      <c r="B121" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C121" s="22"/>
-      <c r="D121" s="22"/>
-      <c r="E121" s="22"/>
-      <c r="F121" s="22"/>
-      <c r="G121" s="23">
+      <c r="C121" s="1"/>
+      <c r="D121" s="1"/>
+      <c r="E121" s="1"/>
+      <c r="F121" s="1"/>
+      <c r="G121" s="7">
         <v>0.09</v>
       </c>
-      <c r="H121" s="22"/>
-      <c r="I121" s="22" t="s">
+      <c r="H121" s="1"/>
+      <c r="I121" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="J121" s="22"/>
-      <c r="K121" s="22"/>
-      <c r="L121" s="22">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="M121" s="22"/>
-      <c r="N121" s="22"/>
-      <c r="O121" s="22"/>
-      <c r="P121" s="22"/>
-      <c r="Q121" s="22">
-        <v>0</v>
-      </c>
-      <c r="R121" s="22"/>
-      <c r="S121" s="22">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="T121" s="24"/>
+      <c r="J121" s="1"/>
+      <c r="K121" s="1"/>
+      <c r="L121" s="1">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="M121" s="1"/>
+      <c r="N121" s="1"/>
+      <c r="O121" s="1"/>
+      <c r="P121" s="1"/>
+      <c r="Q121" s="1">
+        <v>0</v>
+      </c>
+      <c r="R121" s="1"/>
+      <c r="S121" s="1">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="T121" s="5"/>
       <c r="U121" s="5">
         <f>V121</f>
         <v>30</v>
       </c>
-      <c r="V121" s="25">
+      <c r="V121" s="1">
         <v>30</v>
       </c>
       <c r="W121" s="1" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X121" s="22" t="e">
-        <f t="shared" si="26"/>
+      <c r="X121" s="1" t="e">
+        <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y121" s="22">
-        <v>0</v>
-      </c>
-      <c r="Z121" s="22">
-        <v>0</v>
-      </c>
-      <c r="AA121" s="22">
-        <v>0</v>
-      </c>
-      <c r="AB121" s="22">
-        <v>0</v>
-      </c>
-      <c r="AC121" s="22">
-        <v>0</v>
-      </c>
-      <c r="AD121" s="22">
-        <v>0</v>
-      </c>
-      <c r="AE121" s="22">
-        <v>0</v>
-      </c>
-      <c r="AF121" s="22">
-        <v>0</v>
-      </c>
-      <c r="AG121" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH121" s="22">
-        <v>0</v>
-      </c>
-      <c r="AI121" s="22" t="s">
+      <c r="Y121" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z121" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA121" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB121" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC121" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD121" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE121" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF121" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG121" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH121" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI121" s="1" t="s">
         <v>184</v>
       </c>
       <c r="AJ121" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>3</v>
       </c>
-      <c r="AK121" s="22"/>
-      <c r="AL121" s="22"/>
-      <c r="AM121" s="22"/>
-      <c r="AN121" s="22"/>
-      <c r="AO121" s="22"/>
-      <c r="AP121" s="22"/>
-      <c r="AQ121" s="22"/>
+      <c r="AK121" s="1">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AL121" s="1"/>
+      <c r="AM121" s="1"/>
+      <c r="AN121" s="1"/>
+      <c r="AO121" s="1"/>
+      <c r="AP121" s="1"/>
+      <c r="AQ121" s="1"/>
     </row>
     <row r="122" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A122" s="11" t="s">
@@ -13707,7 +14048,7 @@
       <c r="J122" s="11"/>
       <c r="K122" s="11"/>
       <c r="L122" s="11">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="M122" s="11"/>
@@ -13719,21 +14060,21 @@
       </c>
       <c r="R122" s="11"/>
       <c r="S122" s="11">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="T122" s="13"/>
       <c r="U122" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V122" s="20"/>
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="V122" s="11"/>
       <c r="W122" s="1" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X122" s="11" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y122" s="11">
@@ -13770,10 +14111,13 @@
         <v>43</v>
       </c>
       <c r="AJ122" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AK122" s="1"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AK122" s="1">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="AL122" s="1"/>
       <c r="AM122" s="1"/>
       <c r="AN122" s="1"/>
@@ -13814,7 +14158,7 @@
         <v>266.35000000000002</v>
       </c>
       <c r="L123" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>8.2639999999999532</v>
       </c>
       <c r="M123" s="1"/>
@@ -13826,21 +14170,21 @@
       </c>
       <c r="R123" s="1"/>
       <c r="S123" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>54.922799999999995</v>
       </c>
       <c r="T123" s="5"/>
       <c r="U123" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V123" s="19"/>
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="V123" s="1"/>
       <c r="W123" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>14.790962514656934</v>
       </c>
       <c r="X123" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>14.790962514656934</v>
       </c>
       <c r="Y123" s="1">
@@ -13875,10 +14219,13 @@
       </c>
       <c r="AI123" s="1"/>
       <c r="AJ123" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AK123" s="1"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AK123" s="1">
+        <f t="shared" si="23"/>
+        <v>61.821654545454543</v>
+      </c>
       <c r="AL123" s="1"/>
       <c r="AM123" s="1"/>
       <c r="AN123" s="1"/>
@@ -13919,7 +14266,7 @@
         <v>374.3</v>
       </c>
       <c r="L124" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>14.480999999999995</v>
       </c>
       <c r="M124" s="1"/>
@@ -13931,21 +14278,21 @@
       </c>
       <c r="R124" s="1"/>
       <c r="S124" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>77.756200000000007</v>
       </c>
       <c r="T124" s="5"/>
       <c r="U124" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V124" s="19"/>
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="V124" s="1"/>
       <c r="W124" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>13.968521082563193</v>
       </c>
       <c r="X124" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>13.968521082563193</v>
       </c>
       <c r="Y124" s="1">
@@ -13980,10 +14327,13 @@
       </c>
       <c r="AI124" s="1"/>
       <c r="AJ124" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AK124" s="1"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AK124" s="1">
+        <f t="shared" si="23"/>
+        <v>80.942272727272723</v>
+      </c>
       <c r="AL124" s="1"/>
       <c r="AM124" s="1"/>
       <c r="AN124" s="1"/>
@@ -14024,7 +14374,7 @@
         <v>187.85</v>
       </c>
       <c r="L125" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>-28.943999999999988</v>
       </c>
       <c r="M125" s="1"/>
@@ -14036,21 +14386,21 @@
       </c>
       <c r="R125" s="1"/>
       <c r="S125" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>31.781200000000002</v>
       </c>
       <c r="T125" s="5"/>
       <c r="U125" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V125" s="19"/>
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="V125" s="1"/>
       <c r="W125" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>11.656067108856805</v>
       </c>
       <c r="X125" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>11.656067108856805</v>
       </c>
       <c r="Y125" s="1">
@@ -14085,10 +14435,13 @@
       </c>
       <c r="AI125" s="1"/>
       <c r="AJ125" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AK125" s="1"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AK125" s="1">
+        <f t="shared" si="23"/>
+        <v>28.668945454545455</v>
+      </c>
       <c r="AL125" s="1"/>
       <c r="AM125" s="1"/>
       <c r="AN125" s="1"/>
@@ -14129,7 +14482,7 @@
         <v>1453.6</v>
       </c>
       <c r="L126" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>-14.244999999999891</v>
       </c>
       <c r="M126" s="1"/>
@@ -14147,21 +14500,21 @@
         <v>600</v>
       </c>
       <c r="S126" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>287.87099999999998</v>
       </c>
       <c r="T126" s="5"/>
       <c r="U126" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V126" s="19"/>
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="V126" s="1"/>
       <c r="W126" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>18.943026563981785</v>
       </c>
       <c r="X126" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>18.943026563981785</v>
       </c>
       <c r="Y126" s="1">
@@ -14198,10 +14551,13 @@
         <v>167</v>
       </c>
       <c r="AJ126" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AK126" s="1"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AK126" s="1">
+        <f t="shared" si="23"/>
+        <v>186.56694545454545</v>
+      </c>
       <c r="AL126" s="1"/>
       <c r="AM126" s="1"/>
       <c r="AN126" s="1"/>
@@ -14238,7 +14594,7 @@
         <v>211</v>
       </c>
       <c r="L127" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>-9</v>
       </c>
       <c r="M127" s="1"/>
@@ -14250,7 +14606,7 @@
       </c>
       <c r="R127" s="1"/>
       <c r="S127" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>40.4</v>
       </c>
       <c r="T127" s="5">
@@ -14258,16 +14614,16 @@
         <v>238.19999999999996</v>
       </c>
       <c r="U127" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>238.19999999999996</v>
       </c>
-      <c r="V127" s="19"/>
+      <c r="V127" s="1"/>
       <c r="W127" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>9</v>
       </c>
       <c r="X127" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>3.1039603960396041</v>
       </c>
       <c r="Y127" s="1">
@@ -14304,10 +14660,13 @@
         <v>169</v>
       </c>
       <c r="AJ127" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>60</v>
       </c>
-      <c r="AK127" s="1"/>
+      <c r="AK127" s="1">
+        <f t="shared" si="23"/>
+        <v>5.2363636363636354</v>
+      </c>
       <c r="AL127" s="1"/>
       <c r="AM127" s="1"/>
       <c r="AN127" s="1"/>
@@ -14346,7 +14705,7 @@
         <v>180</v>
       </c>
       <c r="L128" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>4</v>
       </c>
       <c r="M128" s="1"/>
@@ -14358,7 +14717,7 @@
       </c>
       <c r="R128" s="1"/>
       <c r="S128" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>36.799999999999997</v>
       </c>
       <c r="T128" s="5">
@@ -14366,16 +14725,16 @@
         <v>214.2</v>
       </c>
       <c r="U128" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>214.2</v>
       </c>
-      <c r="V128" s="19"/>
+      <c r="V128" s="1"/>
       <c r="W128" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>9</v>
       </c>
       <c r="X128" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>3.179347826086957</v>
       </c>
       <c r="Y128" s="1">
@@ -14412,10 +14771,13 @@
         <v>169</v>
       </c>
       <c r="AJ128" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>70</v>
       </c>
-      <c r="AK128" s="1"/>
+      <c r="AK128" s="1">
+        <f t="shared" si="23"/>
+        <v>4.8</v>
+      </c>
       <c r="AL128" s="1"/>
       <c r="AM128" s="1"/>
       <c r="AN128" s="1"/>
@@ -14452,7 +14814,7 @@
         <v>151</v>
       </c>
       <c r="L129" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="M129" s="1"/>
@@ -14464,7 +14826,7 @@
       </c>
       <c r="R129" s="1"/>
       <c r="S129" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>30.2</v>
       </c>
       <c r="T129" s="5">
@@ -14472,16 +14834,16 @@
         <v>170.4</v>
       </c>
       <c r="U129" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>170.4</v>
       </c>
-      <c r="V129" s="19"/>
+      <c r="V129" s="1"/>
       <c r="W129" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>7</v>
       </c>
       <c r="X129" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1.3576158940397351</v>
       </c>
       <c r="Y129" s="1">
@@ -14518,10 +14880,13 @@
         <v>169</v>
       </c>
       <c r="AJ129" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>43</v>
       </c>
-      <c r="AK129" s="1"/>
+      <c r="AK129" s="1">
+        <f t="shared" si="23"/>
+        <v>3.6</v>
+      </c>
       <c r="AL129" s="1"/>
       <c r="AM129" s="1"/>
       <c r="AN129" s="1"/>
@@ -14562,7 +14927,7 @@
         <v>279</v>
       </c>
       <c r="L130" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>-152</v>
       </c>
       <c r="M130" s="1"/>
@@ -14574,21 +14939,21 @@
       </c>
       <c r="R130" s="1"/>
       <c r="S130" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>25.4</v>
       </c>
       <c r="T130" s="5"/>
       <c r="U130" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V130" s="19"/>
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="V130" s="1"/>
       <c r="W130" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>43.465551181102349</v>
       </c>
       <c r="X130" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>43.465551181102349</v>
       </c>
       <c r="Y130" s="1">
@@ -14623,10 +14988,13 @@
       </c>
       <c r="AI130" s="1"/>
       <c r="AJ130" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AK130" s="1"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AK130" s="1">
+        <f t="shared" si="23"/>
+        <v>69.927272727272722</v>
+      </c>
       <c r="AL130" s="1"/>
       <c r="AM130" s="1"/>
       <c r="AN130" s="1"/>
@@ -14667,7 +15035,7 @@
         <v>488</v>
       </c>
       <c r="L131" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>-23</v>
       </c>
       <c r="M131" s="1"/>
@@ -14679,24 +15047,24 @@
       </c>
       <c r="R131" s="1"/>
       <c r="S131" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>93</v>
       </c>
       <c r="T131" s="5">
-        <f t="shared" ref="T131:T134" si="29">10.5*S131-R131-Q131-P131-O131-F131</f>
+        <f t="shared" ref="T131:T134" si="31">10.5*S131-R131-Q131-P131-O131-F131</f>
         <v>283.62300000000039</v>
       </c>
       <c r="U131" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>283.62300000000039</v>
       </c>
-      <c r="V131" s="19"/>
+      <c r="V131" s="1"/>
       <c r="W131" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>10.5</v>
       </c>
       <c r="X131" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>7.4502903225806412</v>
       </c>
       <c r="Y131" s="1">
@@ -14731,10 +15099,13 @@
       </c>
       <c r="AI131" s="1"/>
       <c r="AJ131" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>85</v>
       </c>
-      <c r="AK131" s="1"/>
+      <c r="AK131" s="1">
+        <f t="shared" si="23"/>
+        <v>62.927272727272722</v>
+      </c>
       <c r="AL131" s="1"/>
       <c r="AM131" s="1"/>
       <c r="AN131" s="1"/>
@@ -14775,7 +15146,7 @@
         <v>280.2</v>
       </c>
       <c r="L132" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>10.524000000000001</v>
       </c>
       <c r="M132" s="1"/>
@@ -14787,21 +15158,21 @@
       </c>
       <c r="R132" s="1"/>
       <c r="S132" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>58.144799999999996</v>
       </c>
       <c r="T132" s="5"/>
       <c r="U132" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="V132" s="19"/>
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="V132" s="1"/>
       <c r="W132" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>13.194209989543344</v>
       </c>
       <c r="X132" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>13.194209989543344</v>
       </c>
       <c r="Y132" s="1">
@@ -14836,10 +15207,13 @@
       </c>
       <c r="AI132" s="1"/>
       <c r="AJ132" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AK132" s="1"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AK132" s="1">
+        <f t="shared" si="23"/>
+        <v>56.398927272727271</v>
+      </c>
       <c r="AL132" s="1"/>
       <c r="AM132" s="1"/>
       <c r="AN132" s="1"/>
@@ -14880,7 +15254,7 @@
         <v>324</v>
       </c>
       <c r="L133" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>-7</v>
       </c>
       <c r="M133" s="1"/>
@@ -14892,23 +15266,23 @@
       </c>
       <c r="R133" s="1"/>
       <c r="S133" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>63.4</v>
       </c>
       <c r="T133" s="5">
         <v>120</v>
       </c>
       <c r="U133" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>120</v>
       </c>
-      <c r="V133" s="19"/>
+      <c r="V133" s="1"/>
       <c r="W133" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>9.7791798107255516</v>
       </c>
       <c r="X133" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>7.8864353312302837</v>
       </c>
       <c r="Y133" s="1">
@@ -14943,10 +15317,13 @@
       </c>
       <c r="AI133" s="1"/>
       <c r="AJ133" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>36</v>
       </c>
-      <c r="AK133" s="1"/>
+      <c r="AK133" s="1">
+        <f t="shared" si="23"/>
+        <v>54.709090909090918</v>
+      </c>
       <c r="AL133" s="1"/>
       <c r="AM133" s="1"/>
       <c r="AN133" s="1"/>
@@ -14987,7 +15364,7 @@
         <v>63</v>
       </c>
       <c r="L134" s="1">
-        <f t="shared" ref="L134:L135" si="30">E134-K134</f>
+        <f t="shared" ref="L134:L135" si="32">E134-K134</f>
         <v>-4</v>
       </c>
       <c r="M134" s="1"/>
@@ -14999,24 +15376,24 @@
       </c>
       <c r="R134" s="1"/>
       <c r="S134" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>11.8</v>
       </c>
       <c r="T134" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>62.900000000000006</v>
       </c>
       <c r="U134" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>62.900000000000006</v>
       </c>
-      <c r="V134" s="19"/>
+      <c r="V134" s="1"/>
       <c r="W134" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>10.5</v>
       </c>
       <c r="X134" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>5.1694915254237284</v>
       </c>
       <c r="Y134" s="1">
@@ -15051,10 +15428,13 @@
       </c>
       <c r="AI134" s="1"/>
       <c r="AJ134" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>8</v>
       </c>
-      <c r="AK134" s="1"/>
+      <c r="AK134" s="1">
+        <f t="shared" si="23"/>
+        <v>7.963636363636363</v>
+      </c>
       <c r="AL134" s="1"/>
       <c r="AM134" s="1"/>
       <c r="AN134" s="1"/>
@@ -15093,7 +15473,7 @@
         <v>4</v>
       </c>
       <c r="L135" s="11">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="M135" s="11"/>
@@ -15103,21 +15483,21 @@
       <c r="Q135" s="11"/>
       <c r="R135" s="11"/>
       <c r="S135" s="11">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="T135" s="13"/>
       <c r="U135" s="5">
-        <f t="shared" ref="U135" si="31">T135</f>
-        <v>0</v>
-      </c>
-      <c r="V135" s="20"/>
+        <f t="shared" ref="U135" si="33">T135</f>
+        <v>0</v>
+      </c>
+      <c r="V135" s="11"/>
       <c r="W135" s="1">
-        <f t="shared" ref="W135" si="32">(F135+O135+P135+Q135+R135+U135)/S135</f>
+        <f t="shared" ref="W135" si="34">(F135+O135+P135+Q135+R135+U135)/S135</f>
         <v>15</v>
       </c>
       <c r="X135" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>15</v>
       </c>
       <c r="Y135" s="11">
@@ -15152,10 +15532,13 @@
       </c>
       <c r="AI135" s="11"/>
       <c r="AJ135" s="1">
-        <f t="shared" ref="AJ135" si="33">ROUND(G135*U135,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AK135" s="1"/>
+        <f t="shared" ref="AJ135" si="35">ROUND(G135*U135,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AK135" s="1">
+        <f t="shared" ref="AK135" si="36">(SUM(Y135:AH135)+S135)/11</f>
+        <v>9.0909090909090912E-2</v>
+      </c>
       <c r="AL135" s="1"/>
       <c r="AM135" s="1"/>
       <c r="AN135" s="1"/>
